--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D57E72-0E97-4AD9-B310-CB1FB782857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B60BAC-2C7A-4DA0-A6AC-42D6576F1A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -21,17 +21,26 @@
     <sheet name="fig" sheetId="7" r:id="rId6"/>
     <sheet name="info" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -195,24 +204,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -225,7 +234,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -246,9 +255,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -270,11 +284,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -282,44 +296,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -337,7 +352,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -452,6 +467,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -459,7 +480,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -522,6 +543,12 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -632,6 +659,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -639,7 +672,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -702,6 +735,12 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -812,6 +851,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -819,7 +864,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -882,6 +927,12 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -992,6 +1043,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1062,6 +1119,12 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1160,7 +1223,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1279,7 +1342,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1394,6 +1457,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1465,6 +1534,12 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1574,6 +1649,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1645,6 +1726,12 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.17</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.1599999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1754,6 +1841,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1825,6 +1918,12 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2042,7 +2141,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2157,6 +2256,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2304,6 +2409,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2451,6 +2562,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2522,6 +2639,12 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.29499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2740,7 +2863,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2855,6 +2978,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2926,6 +3055,12 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3035,6 +3170,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3105,6 +3246,12 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3322,7 +3469,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3437,6 +3584,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3507,6 +3660,12 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -3617,6 +3776,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3687,6 +3852,12 @@
                   <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3797,6 +3968,12 @@
                 <c:pt idx="20">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3867,6 +4044,12 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -7320,1172 +7503,1273 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9" style="10"/>
-    <col min="15" max="16" width="9" style="11"/>
-    <col min="17" max="21" width="9" style="12"/>
+    <col min="1" max="1" width="12.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9" style="16"/>
+    <col min="15" max="16" width="9" style="17"/>
+    <col min="17" max="21" width="9" style="13"/>
+    <col min="22" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="3" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="7">
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>46043</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>46043</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="14">
         <v>54</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="14">
         <v>50</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="14">
         <v>53</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="14">
         <v>52</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="14">
         <v>49</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="14">
         <v>52</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="14">
         <v>51</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="14">
         <v>50</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="14">
         <v>50</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="14">
         <v>22</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="15">
         <v>13.1</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="15">
         <v>17.5</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="7">
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>46050</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>46050</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="14">
         <v>54</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="14">
         <v>50</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="14">
         <v>53</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="14">
         <v>52</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="14">
         <v>49</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="14">
         <v>52</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="14">
         <v>51</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="14">
         <v>50</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="14">
         <v>50</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="14">
         <v>22</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="15">
         <v>13.1</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="15">
         <v>17.5</v>
       </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="7">
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>46057</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>46057</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="16">
         <v>54</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="14">
         <v>50</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="16">
         <v>53</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="16">
         <v>52</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="16">
         <v>49</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="16">
         <v>52</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="16">
         <v>51</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="14">
         <v>50</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="14">
         <v>50</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="16">
         <v>22</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="17">
         <v>13.1</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="7">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>46064</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>46064</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="16">
         <v>54</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="14">
         <v>50</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="16">
         <v>53</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="16">
         <v>52</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="16">
         <v>49</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="16">
         <v>52</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="16">
         <v>51</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="14">
         <v>50</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="14">
         <v>50</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="16">
         <v>22</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="17">
         <v>13.1</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="7">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>46078</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>46078</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="16">
         <v>54</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="14">
         <v>50</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="16">
         <v>53</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="16">
         <v>52</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="16">
         <v>49</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="16">
         <v>52</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="16">
         <v>51</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="14">
         <v>50</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="14">
         <v>50</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="16">
         <v>22</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="17">
         <v>13.1</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="7">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>46085</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>46085</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="16">
         <v>54</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="14">
         <v>50</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="16">
         <v>53</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="16">
         <v>52</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="16">
         <v>49</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="16">
         <v>52</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="16">
         <v>51</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="14">
         <v>50</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="14">
         <v>50</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="16">
         <v>22</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="17">
         <v>13.1</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="7">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>46092</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>46092</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="16">
         <v>53</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="16">
         <v>43</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="16">
         <v>47</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="16">
         <v>52</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="16">
         <v>42</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="16">
         <v>45</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="16">
         <v>45</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="16">
         <v>43</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="16">
         <v>44</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="16">
         <v>22</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="17">
         <v>13.1</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="7">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>46099</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>46099</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="16">
         <v>47</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="16">
         <v>41</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="16">
         <v>45</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="16">
         <v>45</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="16">
         <v>39</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="16">
         <v>43</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="16">
         <v>42</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="16">
         <v>39</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="16">
         <v>40</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="16">
         <v>22</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="17">
         <v>13.1</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="7">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>46106</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>46106</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="16">
         <v>39</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="16">
         <v>37</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="16">
         <v>39</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="16">
         <v>37</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="16">
         <v>35</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="16">
         <v>37</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="16">
         <v>37</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="16">
         <v>35</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="16">
         <v>37</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="16">
         <v>22</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="17">
         <v>13.1</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="7">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>46113</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>46113</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="16">
         <v>39</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="16">
         <v>37</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="16">
         <v>39</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="16">
         <v>37</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="16">
         <v>35</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="16">
         <v>37</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="16">
         <v>37</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="16">
         <v>35</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="16">
         <v>37</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="16">
         <v>22</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="17">
         <v>13.1</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="7">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>46120</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>46120</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="16">
         <v>39</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="16">
         <v>37</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="16">
         <v>39</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="16">
         <v>37</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="16">
         <v>35</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="16">
         <v>37</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="16">
         <v>37</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="16">
         <v>35</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="16">
         <v>37</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="16">
         <v>22</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="17">
         <v>13.1</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="7">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>46127</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>46127</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="16">
         <v>39</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="16">
         <v>35</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="16">
         <v>37</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="16">
         <v>37</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="16">
         <v>33</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="16">
         <v>35</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="16">
         <v>36</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="16">
         <v>32</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="16">
         <v>34</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="16">
         <v>22</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="17">
         <v>13.1</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="7">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>46134</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="10">
         <v>46134</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="16">
         <v>39</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="16">
         <v>35</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="16">
         <v>37</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="16">
         <v>37</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="16">
         <v>33</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="16">
         <v>35</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="16">
         <v>36</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="16">
         <v>32</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="16">
         <v>34</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="16">
         <v>22</v>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="17">
         <v>13.1</v>
       </c>
-      <c r="P15" s="11">
+      <c r="P15" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="7">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>46141</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="10">
         <v>46141</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="16">
         <v>39</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="16">
         <v>35</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="16">
         <v>37</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="16">
         <v>37</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="16">
         <v>33</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="16">
         <v>35</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="16">
         <v>36</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="16">
         <v>32</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="16">
         <v>34</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="16">
         <v>22</v>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="17">
         <v>13.1</v>
       </c>
-      <c r="P16" s="11">
+      <c r="P16" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="7">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>46155</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="10">
         <v>46155</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="16">
         <v>39</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="16">
         <v>35</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="16">
         <v>37</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="16">
         <v>37</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="16">
         <v>33</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="16">
         <v>35</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="16">
         <v>36</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="16">
         <v>32</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="16">
         <v>34</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="16">
         <v>22</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="17">
         <v>13.1</v>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="7">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
         <v>46164</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="10">
         <v>46164</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="16">
         <v>39</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="16">
         <v>35</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="16">
         <v>37</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="16">
         <v>37</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="16">
         <v>33</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="16">
         <v>35</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="16">
         <v>36</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="16">
         <v>32</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="16">
         <v>34</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="16">
         <v>22</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="17">
         <v>13.1</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="7">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
         <v>46169</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <v>46169</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="16">
         <v>39</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="16">
         <v>35</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="16">
         <v>37</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="16">
         <v>37</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="16">
         <v>33</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="16">
         <v>35</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="16">
         <v>36</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="16">
         <v>32</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="16">
         <v>34</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="16">
         <v>22</v>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="17">
         <v>13.1</v>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="7">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
         <v>46176</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <v>46176</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="16">
         <v>39</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="16">
         <v>35</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="16">
         <v>37</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="16">
         <v>37</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="16">
         <v>33</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="16">
         <v>35</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="16">
         <v>36</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="16">
         <v>32</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="16">
         <v>34</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="16">
         <v>22</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="17">
         <v>13.1</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="7">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
         <v>46183</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>46183</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="16">
         <v>37</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="16">
         <v>35</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="16">
         <v>36</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="16">
         <v>35</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="16">
         <v>33</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="16">
         <v>34</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="16">
         <v>33</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="16">
         <v>31</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="16">
         <v>32</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="16">
         <v>22</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="17">
         <v>13.1</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="7">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
         <v>46190</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <v>46190</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="16">
         <v>36</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="16">
         <v>34</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="16">
         <v>35</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="16">
         <v>34</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="16">
         <v>32</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="16">
         <v>33</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="16">
         <v>32</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="16">
         <v>31</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="16">
         <v>31</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="16">
         <v>22</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="17">
         <v>13.1</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="17">
         <v>17.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="7">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>46197</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>46197</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="16">
         <v>34</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="16">
         <v>33</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="16">
         <v>33.5</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="16">
         <v>33</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="16">
         <v>32</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="16">
         <v>32.5</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="16">
         <v>32</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="16">
         <v>30</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="16">
         <v>31</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="16">
         <v>22</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="17">
         <v>13.1</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="17">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="16">
+        <v>34</v>
+      </c>
+      <c r="F24" s="16">
+        <v>33</v>
+      </c>
+      <c r="G24" s="16">
+        <v>33.5</v>
+      </c>
+      <c r="H24" s="16">
+        <v>33</v>
+      </c>
+      <c r="I24" s="16">
+        <v>32</v>
+      </c>
+      <c r="J24" s="16">
+        <v>32.5</v>
+      </c>
+      <c r="K24" s="16">
+        <v>32</v>
+      </c>
+      <c r="L24" s="16">
+        <v>30</v>
+      </c>
+      <c r="M24" s="16">
+        <v>31</v>
+      </c>
+      <c r="N24" s="16">
+        <v>22</v>
+      </c>
+      <c r="O24" s="17">
+        <v>13.1</v>
+      </c>
+      <c r="P24" s="17">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="16">
+        <v>34</v>
+      </c>
+      <c r="F25" s="16">
+        <v>33</v>
+      </c>
+      <c r="G25" s="16">
+        <v>33.5</v>
+      </c>
+      <c r="H25" s="16">
+        <v>33</v>
+      </c>
+      <c r="I25" s="16">
+        <v>32</v>
+      </c>
+      <c r="J25" s="16">
+        <v>32.5</v>
+      </c>
+      <c r="K25" s="16">
+        <v>32</v>
+      </c>
+      <c r="L25" s="16">
+        <v>30</v>
+      </c>
+      <c r="M25" s="16">
+        <v>31</v>
+      </c>
+      <c r="N25" s="16">
+        <v>22</v>
+      </c>
+      <c r="O25" s="17">
+        <v>13.1</v>
+      </c>
+      <c r="P25" s="17">
         <v>17.5</v>
       </c>
     </row>
@@ -8504,976 +8788,1059 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="12"/>
+    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="13"/>
+    <col min="22" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="6" t="s">
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="7">
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>46043</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>46043</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="8">
         <v>1.35</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="8">
         <v>1.25</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="8">
         <v>1.3</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="8">
         <v>1.65</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="8">
         <v>1.55</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="8">
         <v>1.6</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="8">
         <v>1.45</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="8">
         <v>1.35</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="8">
         <v>1.4</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="7">
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>46050</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>46050</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="8">
         <v>1.35</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>1.2</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>1.3</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="8">
         <v>1.65</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="8">
         <v>1.5</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="8">
         <v>1.6</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="8">
         <v>1.45</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="8">
         <v>1.3</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="8">
         <v>1.4</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="7">
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>46057</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>46057</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>1.25</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <v>1.2</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <v>1.55</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <v>1.4</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="13">
         <v>1.5</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="13">
         <v>1.35</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="13">
         <v>1.2</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="13">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="7">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>46064</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>46064</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>1.25</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <v>1.2</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <v>1.55</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <v>1.4</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="13">
         <v>1.5</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="13">
         <v>1.35</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="13">
         <v>1.2</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="13">
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="7">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>46078</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>46078</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>1.25</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <v>1.2</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <v>1.55</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <v>1.4</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="13">
         <v>1.5</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="13">
         <v>1.35</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="13">
         <v>1.2</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="13">
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="7">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>46085</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>46085</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <v>1.05</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <v>1.05</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <v>1.4</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <v>1.35</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="13">
         <v>1.35</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="13">
         <v>1.2</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="13">
         <v>1.1499999999999999</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="13">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="7">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>46092</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>46092</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>1</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>1.05</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <v>1.05</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <v>1.35</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <v>1.33</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="13">
         <v>1.35</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="13">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="13">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="7">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>46099</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>46099</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>1.05</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>1</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <v>1</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <v>1.35</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <v>1.3</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="13">
         <v>1.3</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="13">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="13">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="7">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>46106</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>46106</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>1</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>0.98</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <v>1</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <v>1.3</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <v>1.25</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="13">
         <v>1.25</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="13">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="13">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="7">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>46113</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>46113</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>0.98</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>0.95</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <v>0.98</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <v>1.3</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <v>1.23</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="13">
         <v>1.25</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="13">
         <v>1.05</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <v>1.02</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="13">
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="7">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>46120</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>46120</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>0.95</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>0.9</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>0.93</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>1.25</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <v>1.2</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="13">
         <v>1.23</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="13">
         <v>1.05</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="13">
         <v>1</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="7">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>46127</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>46127</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <v>0.95</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>0.9</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <v>0.92</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <v>1.25</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <v>1.2</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="13">
         <v>1.23</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="13">
         <v>1.05</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="13">
         <v>1</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="7">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>46134</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="10">
         <v>46134</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <v>0.95</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <v>0.9</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <v>0.92</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <v>1.25</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <v>1.2</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="13">
         <v>1.23</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="13">
         <v>1.05</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="13">
         <v>1</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="7">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>46141</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="10">
         <v>46141</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>0.95</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <v>0.9</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <v>0.92</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <v>1.25</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <v>1.2</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="13">
         <v>1.23</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="13">
         <v>1.05</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="13">
         <v>1</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="7">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>46155</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="10">
         <v>46155</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <v>0.95</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>0.9</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <v>0.92</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <v>1.25</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <v>1.2</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="13">
         <v>1.23</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="13">
         <v>1.05</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="13">
         <v>1</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="7">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
         <v>46164</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="10">
         <v>46164</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <v>0.95</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <v>0.9</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <v>0.92</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <v>1.25</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <v>1.2</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="13">
         <v>1.23</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="13">
         <v>1.05</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="13">
         <v>1</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="7">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
         <v>46169</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <v>46169</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <v>0.95</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>0.9</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <v>0.92</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <v>1.25</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <v>1.2</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="13">
         <v>1.23</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="13">
         <v>1.05</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="13">
         <v>1</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="13">
         <v>1.03</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="7">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
         <v>46176</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <v>46176</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <v>0.9</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <v>0.88</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <v>0.9</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <v>1.2</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <v>1.18</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="13">
         <v>1.2</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="13">
         <v>1</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="13">
         <v>0.98</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="7">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
         <v>46183</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>46183</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <v>0.9</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <v>0.88</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="13">
         <v>0.88</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="13">
         <v>1.2</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="13">
         <v>1.17</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="13">
         <v>1.18</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="13">
         <v>1</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="13">
         <v>0.98</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="13">
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="7">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
         <v>46190</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <v>46190</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <v>0.9</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <v>0.88</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="13">
         <v>0.88</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <v>1.2</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <v>1.17</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="13">
         <v>1.18</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="13">
         <v>1</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="13">
         <v>0.98</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="13">
         <v>0.98</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="7">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>46197</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>46197</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <v>0.9</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <v>0.88</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="13">
         <v>0.88</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="13">
         <v>1.2</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="13">
         <v>1.17</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="13">
         <v>1.18</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="13">
         <v>1</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="13">
         <v>0.98</v>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="13">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.89</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.86</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="H24" s="13">
+        <v>1.19</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="J24" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="K24" s="13">
+        <v>0.99</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="M24" s="13">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0.86</v>
+      </c>
+      <c r="H25" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="I25" s="13">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J25" s="13">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K25" s="13">
+        <v>0.97</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0.95</v>
+      </c>
+      <c r="M25" s="13">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -9490,976 +9857,1059 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="12"/>
+    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="13"/>
+    <col min="22" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="6" t="s">
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="7">
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>46043</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>46043</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="8">
         <v>0.42</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="8">
         <v>0.41</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="8">
         <v>0.41</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="8">
         <v>0.42</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="8">
         <v>0.41</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="8">
         <v>0.41</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="8">
         <v>0.42</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="8">
         <v>0.41</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="8">
         <v>0.41</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="7">
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>46050</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>46050</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="8">
         <v>0.43</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>0.41</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>0.42</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="8">
         <v>0.43</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="8">
         <v>0.41</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="8">
         <v>0.42</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="8">
         <v>0.43</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="8">
         <v>0.41</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="8">
         <v>0.42</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="7">
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>46057</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>46057</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>0.43</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <v>0.41</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <v>0.42</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <v>0.43</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <v>0.41</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="13">
         <v>0.42</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="13">
         <v>0.43</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="13">
         <v>0.41</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="13">
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="7">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>46064</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>46064</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>0.43</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <v>0.41</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <v>0.42</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <v>0.43</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <v>0.41</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="13">
         <v>0.42</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="8">
         <v>0.43</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="8">
         <v>0.41</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="8">
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="7">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>46078</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>46078</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>0.43</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <v>0.41</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <v>0.42</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <v>0.43</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <v>0.41</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="13">
         <v>0.42</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="13">
         <v>0.43</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="13">
         <v>0.41</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="13">
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="7">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>46085</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>46085</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>0.43</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <v>0.41</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <v>0.42</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <v>0.43</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <v>0.41</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="13">
         <v>0.42</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="13">
         <v>0.43</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="13">
         <v>0.41</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="13">
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="7">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>46092</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>46092</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>0.42</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>0.4</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <v>0.41</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <v>0.42</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <v>0.4</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="13">
         <v>0.41</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="13">
         <v>0.42</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="13">
         <v>0.4</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="13">
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="7">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>46099</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>46099</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>0.41</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>0.39</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <v>0.4</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <v>0.41</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <v>0.39</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="13">
         <v>0.4</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="13">
         <v>0.41</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="13">
         <v>0.39500000000000002</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="13">
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="7">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>46106</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>46106</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>0.39500000000000002</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>0.38</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <v>0.39</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <v>0.39</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <v>0.38</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="13">
         <v>0.39</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="13">
         <v>0.39500000000000002</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="13">
         <v>0.38</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="13">
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="7">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>46113</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>46113</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>0.37</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>0.35</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <v>0.36</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <v>0.37</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <v>0.35</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="13">
         <v>0.36</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="13">
         <v>0.37</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <v>0.35</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="13">
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="7">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>46120</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>46120</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>0.36</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>0.34</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>0.35499999999999998</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>0.36</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <v>0.34</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="13">
         <v>0.35499999999999998</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="13">
         <v>0.36</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="13">
         <v>0.35</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="13">
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="7">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>46127</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>46127</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <v>0.34</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>0.33</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <v>0.34</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <v>0.34</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <v>0.33</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="13">
         <v>0.34</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="13">
         <v>0.34</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="13">
         <v>0.33</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="13">
         <v>0.34</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="7">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>46134</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="10">
         <v>46134</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <v>0.34</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <v>0.33</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <v>0.34</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <v>0.33</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="13">
         <v>0.34</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="13">
         <v>0.33</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="13">
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="7">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>46141</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="10">
         <v>46141</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <v>0.33</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <v>0.33</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <v>0.33</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="13">
         <v>0.33</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="13">
         <v>0.33</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="7">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>46155</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="10">
         <v>46155</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>0.33</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <v>0.33</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <v>0.33</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="13">
         <v>0.33</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="13">
         <v>0.33</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="7">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
         <v>46164</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="10">
         <v>46164</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <v>0.33</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <v>0.33</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <v>0.33</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="13">
         <v>0.33</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="13">
         <v>0.33</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="7">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
         <v>46169</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <v>46169</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>0.33</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <v>0.33</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <v>0.33</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="13">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="13">
         <v>0.33</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="13">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="7">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
         <v>46176</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <v>46176</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <v>0.33</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <v>0.32500000000000001</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <v>0.33</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <v>0.33</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <v>0.32500000000000001</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="13">
         <v>0.33</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="13">
         <v>0.33</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="13">
         <v>0.32500000000000001</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="13">
         <v>0.33</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="7">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
         <v>46183</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>46183</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <v>0.31</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <v>0.3</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="13">
         <v>0.30499999999999999</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="13">
         <v>0.32500000000000001</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="13">
         <v>0.315</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="13">
         <v>0.32</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="13">
         <v>0.32</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="13">
         <v>0.31</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="13">
         <v>0.315</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="7">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
         <v>46190</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <v>46190</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <v>0.29499999999999998</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <v>0.31</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <v>0.3</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="13">
         <v>0.30499999999999999</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="13">
         <v>0.3</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="13">
         <v>0.29499999999999998</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="13">
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="7">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>46197</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>46197</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <v>0.29499999999999998</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="13">
         <v>0.30499999999999999</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="13">
         <v>0.29499999999999998</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="13">
         <v>0.3</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="13">
         <v>0.3</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="13">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="13">
         <v>0.29499999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="J24" s="13">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K24" s="13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="M24" s="13">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="H25" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="J25" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="K25" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="M25" s="13">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -10476,780 +10926,845 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="12"/>
+    <col min="1" max="1" width="10.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="13"/>
+    <col min="22" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="6" t="s">
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="7">
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>46043</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>46043</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="8">
         <v>0.82</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="8">
         <v>0.78</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="8">
         <v>0.79</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="8">
         <v>0.75</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="8">
         <v>0.71</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="8">
         <v>0.72</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="7">
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>46050</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>46050</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="8">
         <v>0.85</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>0.78</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>0.79</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="8">
         <v>0.82</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="8">
         <v>0.7</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="8">
         <v>0.76</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="7">
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>46057</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>46057</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>0.85</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <v>0.78</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <v>0.79</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <v>0.82</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <v>0.7</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="7">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>46064</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>46064</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>0.85</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <v>0.78</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <v>0.79</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <v>0.82</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <v>0.7</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="7">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>46078</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>46078</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>0.85</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <v>0.78</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <v>0.79</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <v>0.82</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <v>0.7</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="7">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>46085</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>46085</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>0.85</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <v>0.78</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <v>0.79</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <v>0.82</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <v>0.7</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="7">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>46092</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>46092</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>0.85</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>0.78</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <v>0.79</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <v>0.82</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <v>0.7</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="7">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>46099</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>46099</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>0.85</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>0.78</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <v>0.79</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <v>0.82</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <v>0.7</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="7">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>46106</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>46106</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>0.85</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>0.78</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <v>0.79</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <v>0.82</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <v>0.7</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="7">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>46113</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>46113</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>0.85</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>0.78</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <v>0.79</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <v>0.82</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <v>0.7</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="7">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>46120</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>46120</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>0.85</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>0.78</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>0.79</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>0.82</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <v>0.7</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="7">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>46127</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>46127</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <v>0.85</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>0.78</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <v>0.79</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <v>0.82</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <v>0.7</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="7">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>46134</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="10">
         <v>46134</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <v>0.85</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <v>0.78</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <v>0.79</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <v>0.82</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <v>0.7</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="7">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>46141</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="10">
         <v>46141</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>0.8</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <v>0.75</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <v>0.78</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <v>0.8</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <v>0.75</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="7">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>46155</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="10">
         <v>46155</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <v>0.8</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>0.75</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <v>0.78</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <v>0.8</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <v>0.75</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="7">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
         <v>46164</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="10">
         <v>46164</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <v>0.8</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <v>0.75</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <v>0.78</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <v>0.8</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <v>0.75</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="7">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
         <v>46169</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <v>46169</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <v>0.8</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>0.75</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <v>0.78</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <v>0.8</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <v>0.75</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="7">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
         <v>46176</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <v>46176</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <v>0.78</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <v>0.72</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <v>0.75</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <v>0.8</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <v>0.75</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="7">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
         <v>46183</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>46183</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <v>0.75</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <v>0.72</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="13">
         <v>0.74</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="13">
         <v>0.8</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="13">
         <v>0.75</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="7">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
         <v>46190</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <v>46190</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <v>0.75</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <v>0.7</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="13">
         <v>0.74</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <v>0.8</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="13">
         <v>0.75</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="13">
         <v>0.76</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="7">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>46197</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>46197</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <v>0.74</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <v>0.71</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="13">
         <v>0.73</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="13">
         <v>0.8</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="13">
         <v>0.75</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="13">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.73</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.69</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0.71</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="J24" s="13">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.69</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.66</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0.69</v>
+      </c>
+      <c r="H25" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="J25" s="13">
         <v>0.76</v>
       </c>
     </row>
@@ -11267,977 +11782,1060 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="11" customWidth="1"/>
-    <col min="6" max="13" width="9" style="11"/>
-    <col min="14" max="21" width="9" style="12"/>
+    <col min="1" max="1" width="10.3984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="17" customWidth="1"/>
+    <col min="6" max="13" width="9" style="17"/>
+    <col min="14" max="21" width="9" style="13"/>
+    <col min="22" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="4" t="s">
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="7">
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>46043</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>46043</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="15">
         <v>12</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="15">
         <v>11</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="15">
         <v>11.5</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="15">
         <v>19</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="15">
         <v>18</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="15">
         <v>18.5</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="15">
         <v>10</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="15">
         <v>9</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="15">
         <v>9.5</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="7">
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>46050</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>46050</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="15">
         <v>12</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="15">
         <v>11</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="15">
         <v>11.5</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="15">
         <v>19</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="15">
         <v>18</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="15">
         <v>18.5</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="15">
         <v>10</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="15">
         <v>9</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="15">
         <v>9.5</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="7">
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>46057</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>46057</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="17">
         <v>12</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="17">
         <v>11</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="17">
         <v>11.5</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="17">
         <v>19</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="17">
         <v>18</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="17">
         <v>18.5</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="17">
         <v>10</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="17">
         <v>9</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="7">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>46064</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>46064</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="17">
         <v>12</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="17">
         <v>11</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="17">
         <v>11.5</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="17">
         <v>19</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="17">
         <v>18</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="17">
         <v>18.5</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="17">
         <v>10</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="17">
         <v>9</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="7">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>46078</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>46078</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="17">
         <v>12</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="17">
         <v>11</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="17">
         <v>11.5</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="17">
         <v>19</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="17">
         <v>18</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="17">
         <v>18.5</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="17">
         <v>10</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="17">
         <v>9</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="7">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>46085</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>46085</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="17">
         <v>12</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="17">
         <v>11</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="17">
         <v>11.5</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="17">
         <v>19</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="17">
         <v>18</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="17">
         <v>18.5</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="17">
         <v>10</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="17">
         <v>9</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="7">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>46092</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>46092</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="17">
         <v>12</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="17">
         <v>11</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="17">
         <v>11.5</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="17">
         <v>19</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="17">
         <v>18</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="17">
         <v>18.5</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="17">
         <v>10</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="17">
         <v>9</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="7">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>46099</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>46099</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="17">
         <v>12</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="17">
         <v>11</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="17">
         <v>11.5</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="17">
         <v>19</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="17">
         <v>18</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="17">
         <v>18.5</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="17">
         <v>10</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="17">
         <v>9</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="7">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>46106</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>46106</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="17">
         <v>12</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="17">
         <v>11</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="17">
         <v>11.5</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="17">
         <v>19</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="17">
         <v>18</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="17">
         <v>18.5</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="17">
         <v>10</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="17">
         <v>9</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="7">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>46113</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>46113</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="17">
         <v>12</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="17">
         <v>11</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="17">
         <v>11.5</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="17">
         <v>19</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="17">
         <v>18</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="17">
         <v>18.5</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="17">
         <v>10</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="17">
         <v>9</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="17">
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="7">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>46120</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>46120</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="17">
         <v>11.5</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="17">
         <v>10.5</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="17">
         <v>11</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="17">
         <v>18.5</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="17">
         <v>17.5</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="17">
         <v>18</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="17">
         <v>9.5</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="17">
         <v>8.5</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="7">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>46127</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>46127</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="17">
         <v>11</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="17">
         <v>10</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="17">
         <v>10.5</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="17">
         <v>18.5</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="17">
         <v>17</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="17">
         <v>17.75</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="17">
         <v>9</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="17">
         <v>8.5</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="7">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>46134</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="10">
         <v>46134</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="17">
         <v>11</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="17">
         <v>10</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="17">
         <v>10.5</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="17">
         <v>18.5</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="17">
         <v>17</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="17">
         <v>17.75</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="17">
         <v>9</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="17">
         <v>8.5</v>
       </c>
-      <c r="M15" s="11">
+      <c r="M15" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="7">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>46141</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="10">
         <v>46141</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="17">
         <v>11</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="17">
         <v>10</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="17">
         <v>10.5</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="17">
         <v>18.5</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="17">
         <v>17</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="17">
         <v>17.75</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="17">
         <v>9</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="17">
         <v>8.5</v>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="7">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>46155</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="10">
         <v>46155</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="17">
         <v>11</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="17">
         <v>10</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="17">
         <v>10.5</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="17">
         <v>18.5</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="17">
         <v>17</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="17">
         <v>17.75</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="17">
         <v>9</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="17">
         <v>8.5</v>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="7">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
         <v>46164</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="10">
         <v>46164</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="17">
         <v>11</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="17">
         <v>10</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="17">
         <v>10.5</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="17">
         <v>18.5</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="17">
         <v>17</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="17">
         <v>17.75</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="17">
         <v>9</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="17">
         <v>8.5</v>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="7">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
         <v>46169</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <v>46169</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="17">
         <v>11</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="17">
         <v>10</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="17">
         <v>10.5</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="17">
         <v>18.5</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="17">
         <v>17</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="17">
         <v>17.75</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="17">
         <v>9</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="17">
         <v>8.5</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="7">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
         <v>46176</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <v>46176</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="17">
         <v>11</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="17">
         <v>10</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="17">
         <v>10.5</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="17">
         <v>18.5</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="17">
         <v>17</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="17">
         <v>17.75</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="17">
         <v>9</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="17">
         <v>8.5</v>
       </c>
-      <c r="M20" s="11">
+      <c r="M20" s="17">
         <v>8.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="7">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
         <v>46183</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>46183</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="17">
         <v>10.5</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="17">
         <v>9.5</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="17">
         <v>10</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="17">
         <v>17</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="17">
         <v>16</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="17">
         <v>16.5</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="17">
         <v>8.5</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="17">
         <v>8</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="7">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
         <v>46190</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <v>46190</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="17">
         <v>10.5</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="17">
         <v>9.5</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="17">
         <v>10</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="17">
         <v>17</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="17">
         <v>16</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="17">
         <v>16.5</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="17">
         <v>8.5</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="17">
         <v>8</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="7">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
         <v>46197</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>46197</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="17">
         <v>10.5</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="17">
         <v>9.5</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="17">
         <v>10</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="17">
         <v>17</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="17">
         <v>16</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="17">
         <v>16.5</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="17">
         <v>8.5</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="17">
         <v>8</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="17">
+        <v>10.5</v>
+      </c>
+      <c r="F24" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="G24" s="17">
+        <v>10</v>
+      </c>
+      <c r="H24" s="17">
+        <v>17</v>
+      </c>
+      <c r="I24" s="17">
+        <v>16</v>
+      </c>
+      <c r="J24" s="17">
+        <v>16.5</v>
+      </c>
+      <c r="K24" s="17">
+        <v>8.5</v>
+      </c>
+      <c r="L24" s="17">
+        <v>8</v>
+      </c>
+      <c r="M24" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46211</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="17">
+        <v>10.5</v>
+      </c>
+      <c r="F25" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="G25" s="17">
+        <v>10</v>
+      </c>
+      <c r="H25" s="17">
+        <v>17</v>
+      </c>
+      <c r="I25" s="17">
+        <v>16</v>
+      </c>
+      <c r="J25" s="17">
+        <v>16.5</v>
+      </c>
+      <c r="K25" s="17">
+        <v>8.5</v>
+      </c>
+      <c r="L25" s="17">
+        <v>8</v>
+      </c>
+      <c r="M25" s="17">
         <v>8</v>
       </c>
     </row>
@@ -12256,7 +12854,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12268,18 +12866,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12287,25 +12885,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -12313,19 +12911,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -12333,19 +12931,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -12353,13 +12951,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -12367,13 +12965,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B60BAC-2C7A-4DA0-A6AC-42D6576F1A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CA905C-5792-49E9-8D1E-5C5A4E22435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -204,24 +204,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +234,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -284,7 +284,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -296,45 +296,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,7 +352,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -473,6 +473,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -480,7 +483,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -549,6 +552,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -665,6 +671,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -672,7 +681,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -741,6 +750,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -857,6 +869,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -864,7 +879,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -933,6 +948,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1049,6 +1067,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1125,6 +1146,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1223,7 +1247,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1342,7 +1366,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1463,6 +1487,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1540,6 +1567,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.85</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1655,6 +1685,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1732,6 +1765,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.1499999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1847,6 +1883,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1924,6 +1963,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2141,7 +2183,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2262,6 +2304,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2415,6 +2460,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2568,6 +2616,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2645,6 +2696,9 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.26500000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2863,7 +2917,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2984,6 +3038,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3060,6 +3117,9 @@
                   <c:v>0.71</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>0.69</c:v>
                 </c:pt>
               </c:numCache>
@@ -3176,6 +3236,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3252,6 +3315,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
@@ -3469,7 +3535,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3590,6 +3656,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3666,6 +3735,9 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -3782,6 +3854,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3858,6 +3933,9 @@
                   <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3974,6 +4052,9 @@
                 <c:pt idx="22">
                   <c:v>46211</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>46218</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4050,6 +4131,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -7503,1273 +7587,1323 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9" style="16"/>
-    <col min="15" max="16" width="9" style="17"/>
-    <col min="17" max="21" width="9" style="13"/>
-    <col min="22" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9" style="13"/>
+    <col min="15" max="16" width="9" style="14"/>
+    <col min="17" max="21" width="9" style="10"/>
+    <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="14" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="11">
         <v>54</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="11">
         <v>50</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="11">
         <v>53</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="11">
         <v>52</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="11">
         <v>49</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="11">
         <v>52</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="11">
         <v>51</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="11">
         <v>50</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="11">
         <v>50</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="11">
         <v>22</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="12">
         <v>13.1</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="12">
         <v>17.5</v>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>54</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>50</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="11">
         <v>53</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="11">
         <v>52</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="11">
         <v>49</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="11">
         <v>52</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="11">
         <v>51</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="11">
         <v>50</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="11">
         <v>50</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="11">
         <v>22</v>
       </c>
-      <c r="O4" s="15">
+      <c r="O4" s="12">
         <v>13.1</v>
       </c>
-      <c r="P4" s="15">
+      <c r="P4" s="12">
         <v>17.5</v>
       </c>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="13">
         <v>54</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <v>50</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="13">
         <v>53</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="13">
         <v>52</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="13">
         <v>49</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="13">
         <v>52</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="13">
         <v>51</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="11">
         <v>50</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="11">
         <v>50</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="13">
         <v>22</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="14">
         <v>13.1</v>
       </c>
-      <c r="P5" s="17">
+      <c r="P5" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="6" spans="1:21">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="13">
         <v>54</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="11">
         <v>50</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="13">
         <v>53</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="13">
         <v>52</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="13">
         <v>49</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="13">
         <v>52</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="13">
         <v>51</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="11">
         <v>50</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="11">
         <v>50</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="13">
         <v>22</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="14">
         <v>13.1</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P6" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+    <row r="7" spans="1:21">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <v>54</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <v>50</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="13">
         <v>53</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="13">
         <v>52</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="13">
         <v>49</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="13">
         <v>52</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="13">
         <v>51</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="11">
         <v>50</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="11">
         <v>50</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="13">
         <v>22</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="14">
         <v>13.1</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+    <row r="8" spans="1:21">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="13">
         <v>54</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>50</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="13">
         <v>53</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="13">
         <v>52</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="13">
         <v>49</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="13">
         <v>52</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="13">
         <v>51</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="11">
         <v>50</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="11">
         <v>50</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="13">
         <v>22</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="14">
         <v>13.1</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+    <row r="9" spans="1:21">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="13">
         <v>53</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="13">
         <v>43</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="13">
         <v>47</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="13">
         <v>52</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="13">
         <v>42</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="13">
         <v>45</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="13">
         <v>45</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="13">
         <v>43</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="13">
         <v>44</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="13">
         <v>22</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="14">
         <v>13.1</v>
       </c>
-      <c r="P9" s="17">
+      <c r="P9" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+    <row r="10" spans="1:21">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="13">
         <v>47</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="13">
         <v>41</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="13">
         <v>45</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="13">
         <v>45</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="13">
         <v>39</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="13">
         <v>43</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="13">
         <v>42</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="13">
         <v>39</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="13">
         <v>40</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="13">
         <v>22</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="14">
         <v>13.1</v>
       </c>
-      <c r="P10" s="17">
+      <c r="P10" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:21">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="13">
         <v>39</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="13">
         <v>37</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="13">
         <v>39</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="13">
         <v>37</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="13">
         <v>35</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="13">
         <v>37</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="13">
         <v>37</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="13">
         <v>35</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="13">
         <v>37</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="13">
         <v>22</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="14">
         <v>13.1</v>
       </c>
-      <c r="P11" s="17">
+      <c r="P11" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:21">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="13">
         <v>39</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="13">
         <v>37</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="13">
         <v>39</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="13">
         <v>37</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="13">
         <v>35</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="13">
         <v>37</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="13">
         <v>37</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="13">
         <v>35</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="13">
         <v>37</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="13">
         <v>22</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="14">
         <v>13.1</v>
       </c>
-      <c r="P12" s="17">
+      <c r="P12" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+    <row r="13" spans="1:21">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="13">
         <v>39</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="13">
         <v>37</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="13">
         <v>39</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="13">
         <v>37</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="13">
         <v>35</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="13">
         <v>37</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="13">
         <v>37</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="13">
         <v>35</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="13">
         <v>37</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="13">
         <v>22</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="14">
         <v>13.1</v>
       </c>
-      <c r="P13" s="17">
+      <c r="P13" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+    <row r="14" spans="1:21">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="13">
         <v>39</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="13">
         <v>35</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="13">
         <v>37</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="13">
         <v>37</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="13">
         <v>33</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="13">
         <v>35</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="13">
         <v>36</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="13">
         <v>32</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="13">
         <v>34</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="13">
         <v>22</v>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="14">
         <v>13.1</v>
       </c>
-      <c r="P14" s="17">
+      <c r="P14" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+    <row r="15" spans="1:21">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="13">
         <v>39</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="13">
         <v>35</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="13">
         <v>37</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="13">
         <v>37</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="13">
         <v>33</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="13">
         <v>35</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="13">
         <v>36</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="13">
         <v>32</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="13">
         <v>34</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="13">
         <v>22</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="14">
         <v>13.1</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+    <row r="16" spans="1:21">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="13">
         <v>39</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="13">
         <v>35</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="13">
         <v>37</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="13">
         <v>37</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="13">
         <v>33</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="13">
         <v>35</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="13">
         <v>36</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="13">
         <v>32</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="13">
         <v>34</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="13">
         <v>22</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="14">
         <v>13.1</v>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    <row r="17" spans="1:16">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="13">
         <v>39</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="13">
         <v>35</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="13">
         <v>37</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="13">
         <v>37</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="13">
         <v>33</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="13">
         <v>35</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="13">
         <v>36</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="13">
         <v>32</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="13">
         <v>34</v>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="13">
         <v>22</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="14">
         <v>13.1</v>
       </c>
-      <c r="P17" s="17">
+      <c r="P17" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    <row r="18" spans="1:16">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="13">
         <v>39</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="13">
         <v>35</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="13">
         <v>37</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="13">
         <v>37</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="13">
         <v>33</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="13">
         <v>35</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="13">
         <v>36</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="13">
         <v>32</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="13">
         <v>34</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="13">
         <v>22</v>
       </c>
-      <c r="O18" s="17">
+      <c r="O18" s="14">
         <v>13.1</v>
       </c>
-      <c r="P18" s="17">
+      <c r="P18" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:16">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="13">
         <v>39</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="13">
         <v>35</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="13">
         <v>37</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="13">
         <v>37</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="13">
         <v>33</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="13">
         <v>35</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="13">
         <v>36</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="13">
         <v>32</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="13">
         <v>34</v>
       </c>
-      <c r="N19" s="16">
+      <c r="N19" s="13">
         <v>22</v>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="14">
         <v>13.1</v>
       </c>
-      <c r="P19" s="17">
+      <c r="P19" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    <row r="20" spans="1:16">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="13">
         <v>39</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="13">
         <v>35</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="13">
         <v>37</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="13">
         <v>37</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="13">
         <v>33</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="13">
         <v>35</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="13">
         <v>36</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="13">
         <v>32</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="13">
         <v>34</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="13">
         <v>22</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="14">
         <v>13.1</v>
       </c>
-      <c r="P20" s="17">
+      <c r="P20" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:16">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="13">
         <v>37</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="13">
         <v>35</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="13">
         <v>36</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="13">
         <v>35</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="13">
         <v>33</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="13">
         <v>34</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="13">
         <v>33</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="13">
         <v>31</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="13">
         <v>32</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="13">
         <v>22</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="14">
         <v>13.1</v>
       </c>
-      <c r="P21" s="17">
+      <c r="P21" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+    <row r="22" spans="1:16">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="13">
         <v>36</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="13">
         <v>34</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="13">
         <v>35</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="13">
         <v>34</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="13">
         <v>32</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="13">
         <v>33</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="13">
         <v>32</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="13">
         <v>31</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="13">
         <v>31</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="13">
         <v>22</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="14">
         <v>13.1</v>
       </c>
-      <c r="P22" s="17">
+      <c r="P22" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:16">
+      <c r="A23" s="7">
         <v>46197</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>46197</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="13">
         <v>34</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="13">
         <v>33</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="13">
         <v>33.5</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="13">
         <v>33</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="13">
         <v>32</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="13">
         <v>32.5</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="13">
         <v>32</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="13">
         <v>30</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="13">
         <v>31</v>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="13">
         <v>22</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="14">
         <v>13.1</v>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:16">
+      <c r="A24" s="7">
         <v>46204</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>46204</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="13">
         <v>34</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="13">
         <v>33</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="13">
         <v>33.5</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="13">
         <v>33</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="13">
         <v>32</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="13">
         <v>32.5</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="13">
         <v>32</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="13">
         <v>30</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="13">
         <v>31</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="13">
         <v>22</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="14">
         <v>13.1</v>
       </c>
-      <c r="P24" s="17">
+      <c r="P24" s="14">
         <v>17.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:16">
+      <c r="A25" s="7">
         <v>46211</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>46211</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="13">
         <v>34</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="13">
         <v>33</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="13">
         <v>33.5</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="13">
         <v>33</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="13">
         <v>32</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="13">
         <v>32.5</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="13">
         <v>32</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="13">
         <v>30</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="13">
         <v>31</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="13">
         <v>22</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="14">
         <v>13.1</v>
       </c>
-      <c r="P25" s="17">
+      <c r="P25" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="13">
+        <v>34</v>
+      </c>
+      <c r="F26" s="13">
+        <v>33</v>
+      </c>
+      <c r="G26" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H26" s="13">
+        <v>33</v>
+      </c>
+      <c r="I26" s="13">
+        <v>32</v>
+      </c>
+      <c r="J26" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K26" s="13">
+        <v>32</v>
+      </c>
+      <c r="L26" s="13">
+        <v>30</v>
+      </c>
+      <c r="M26" s="13">
+        <v>31</v>
+      </c>
+      <c r="N26" s="13">
+        <v>22</v>
+      </c>
+      <c r="O26" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P26" s="14">
         <v>17.5</v>
       </c>
     </row>
@@ -8788,1059 +8922,1100 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="13"/>
-    <col min="22" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="10"/>
+    <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="8" t="s">
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>1.35</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <v>1.25</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>1.3</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="5">
         <v>1.65</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <v>1.55</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="5">
         <v>1.6</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="5">
         <v>1.45</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="5">
         <v>1.35</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="5">
         <v>1.4</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="5">
         <v>1.35</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="5">
         <v>1.2</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="5">
         <v>1.3</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="5">
         <v>1.65</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>1.5</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="5">
         <v>1.6</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="5">
         <v>1.45</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="5">
         <v>1.3</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="5">
         <v>1.4</v>
       </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="10">
         <v>1.25</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>1.2</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="10">
         <v>1.55</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="10">
         <v>1.4</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="10">
         <v>1.5</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="10">
         <v>1.35</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="10">
         <v>1.2</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="10">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="6" spans="1:21">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
         <v>1.25</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>1.2</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="10">
         <v>1.55</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="10">
         <v>1.4</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="10">
         <v>1.5</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="10">
         <v>1.35</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="10">
         <v>1.2</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="10">
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+    <row r="7" spans="1:21">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="10">
         <v>1.25</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <v>1.2</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="10">
         <v>1.55</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="10">
         <v>1.4</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="10">
         <v>1.5</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="10">
         <v>1.35</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="10">
         <v>1.2</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="10">
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+    <row r="8" spans="1:21">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>1.05</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <v>1.05</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <v>1.4</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="10">
         <v>1.35</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="10">
         <v>1.35</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="10">
         <v>1.2</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="10">
         <v>1.1499999999999999</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="10">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+    <row r="9" spans="1:21">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="10">
         <v>1</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="10">
         <v>1.05</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="10">
         <v>1.05</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="10">
         <v>1.35</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="10">
         <v>1.33</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="10">
         <v>1.35</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="10">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="10">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+    <row r="10" spans="1:21">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="10">
         <v>1.05</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <v>1</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="10">
         <v>1.35</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="10">
         <v>1.3</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="10">
         <v>1.3</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="10">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="10">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:21">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>1</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>0.98</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <v>1</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="10">
         <v>1.3</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="10">
         <v>1.25</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="10">
         <v>1.25</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="10">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="10">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:21">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="10">
         <v>0.98</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>0.95</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>0.98</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="10">
         <v>1.3</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="10">
         <v>1.23</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="10">
         <v>1.25</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="10">
         <v>1.05</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="10">
         <v>1.02</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="10">
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+    <row r="13" spans="1:21">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="10">
         <v>0.95</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>0.9</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>0.93</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="10">
         <v>1.25</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="10">
         <v>1.2</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="10">
         <v>1.23</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="10">
         <v>1.05</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="10">
         <v>1</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+    <row r="14" spans="1:21">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <v>0.95</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <v>0.9</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <v>0.92</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="10">
         <v>1.25</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <v>1.2</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="10">
         <v>1.23</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="10">
         <v>1.05</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="10">
         <v>1</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+    <row r="15" spans="1:21">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <v>0.95</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <v>0.9</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <v>0.92</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="10">
         <v>1.25</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="10">
         <v>1.2</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="10">
         <v>1.23</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="10">
         <v>1.05</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="10">
         <v>1</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+    <row r="16" spans="1:21">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <v>0.95</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <v>0.9</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <v>0.92</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="10">
         <v>1.25</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="10">
         <v>1.2</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="10">
         <v>1.23</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="10">
         <v>1.05</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="10">
         <v>1</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    <row r="17" spans="1:13">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <v>0.95</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <v>0.9</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <v>0.92</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="10">
         <v>1.25</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
         <v>1.2</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="10">
         <v>1.23</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="10">
         <v>1.05</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="10">
         <v>1</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    <row r="18" spans="1:13">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <v>0.95</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <v>0.9</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <v>0.92</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="10">
         <v>1.25</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="10">
         <v>1.2</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="10">
         <v>1.23</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="10">
         <v>1.05</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="10">
         <v>1</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:13">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <v>0.95</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>0.9</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <v>0.92</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="10">
         <v>1.25</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="10">
         <v>1.2</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="10">
         <v>1.23</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="10">
         <v>1.05</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="10">
         <v>1</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="10">
         <v>1.03</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    <row r="20" spans="1:13">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <v>0.9</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <v>0.88</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <v>0.9</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="10">
         <v>1.2</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <v>1.18</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="10">
         <v>1.2</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="10">
         <v>1</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="10">
         <v>0.98</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:13">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <v>0.9</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <v>0.88</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <v>0.88</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="10">
         <v>1.2</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="10">
         <v>1.17</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="10">
         <v>1.18</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="10">
         <v>1</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="10">
         <v>0.98</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="10">
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+    <row r="22" spans="1:13">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <v>0.9</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <v>0.88</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <v>0.88</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="10">
         <v>1.2</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="10">
         <v>1.17</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="10">
         <v>1.18</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="10">
         <v>1</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="10">
         <v>0.98</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="10">
         <v>0.98</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:13">
+      <c r="A23" s="7">
         <v>46197</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>46197</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <v>0.9</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <v>0.88</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <v>0.88</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="10">
         <v>1.2</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="10">
         <v>1.17</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="10">
         <v>1.18</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="10">
         <v>1</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="10">
         <v>0.98</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="10">
         <v>0.98</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:13">
+      <c r="A24" s="7">
         <v>46204</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>46204</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="10">
         <v>0.89</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="10">
         <v>0.86</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="10">
         <v>0.87</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="10">
         <v>1.19</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="10">
         <v>1.1599999999999999</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="10">
         <v>1.17</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="10">
         <v>0.99</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="10">
         <v>0.96</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="10">
         <v>0.97</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:13">
+      <c r="A25" s="7">
         <v>46211</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>46211</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="10">
         <v>0.87</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="10">
         <v>0.85</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="10">
         <v>0.86</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="10">
         <v>1.17</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="10">
         <v>1.1499999999999999</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="10">
         <v>1.1599999999999999</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="10">
         <v>0.97</v>
       </c>
-      <c r="L25" s="13">
+      <c r="L25" s="10">
         <v>0.95</v>
       </c>
-      <c r="M25" s="13">
+      <c r="M25" s="10">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0.86</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0.84</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="H26" s="10">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I26" s="10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J26" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0.93</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -9857,1059 +10032,1100 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="13"/>
-    <col min="22" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="10"/>
+    <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="8" t="s">
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>0.42</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <v>0.41</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>0.41</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="5">
         <v>0.42</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <v>0.41</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="5">
         <v>0.41</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="5">
         <v>0.42</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="5">
         <v>0.41</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="5">
         <v>0.41</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="5">
         <v>0.43</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="5">
         <v>0.41</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="5">
         <v>0.42</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="5">
         <v>0.43</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>0.41</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="5">
         <v>0.42</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="5">
         <v>0.43</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="5">
         <v>0.41</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="5">
         <v>0.42</v>
       </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="10">
         <v>0.43</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="10">
         <v>0.41</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>0.42</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="10">
         <v>0.43</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="10">
         <v>0.41</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="10">
         <v>0.42</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="10">
         <v>0.43</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="10">
         <v>0.41</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="10">
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="6" spans="1:21">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
         <v>0.43</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>0.41</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>0.42</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="10">
         <v>0.43</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="10">
         <v>0.41</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="10">
         <v>0.42</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="5">
         <v>0.43</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="5">
         <v>0.41</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="5">
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+    <row r="7" spans="1:21">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="10">
         <v>0.43</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>0.41</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <v>0.42</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="10">
         <v>0.43</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="10">
         <v>0.41</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="10">
         <v>0.42</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="10">
         <v>0.43</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="10">
         <v>0.41</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="10">
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+    <row r="8" spans="1:21">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>0.43</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>0.41</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <v>0.42</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <v>0.43</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="10">
         <v>0.41</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="10">
         <v>0.42</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="10">
         <v>0.43</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="10">
         <v>0.41</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="10">
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+    <row r="9" spans="1:21">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="10">
         <v>0.42</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="10">
         <v>0.4</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="10">
         <v>0.41</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="10">
         <v>0.42</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="10">
         <v>0.4</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="10">
         <v>0.41</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="10">
         <v>0.42</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="10">
         <v>0.4</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="10">
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+    <row r="10" spans="1:21">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="10">
         <v>0.41</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>0.39</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <v>0.4</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="10">
         <v>0.41</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="10">
         <v>0.39</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="10">
         <v>0.4</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="10">
         <v>0.41</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="10">
         <v>0.39500000000000002</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="10">
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:21">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>0.39500000000000002</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>0.38</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <v>0.39</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="10">
         <v>0.39</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="10">
         <v>0.38</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="10">
         <v>0.39</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="10">
         <v>0.39500000000000002</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="10">
         <v>0.38</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="10">
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:21">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="10">
         <v>0.37</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>0.35</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>0.36</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="10">
         <v>0.37</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="10">
         <v>0.35</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="10">
         <v>0.36</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="10">
         <v>0.37</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="10">
         <v>0.35</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="10">
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+    <row r="13" spans="1:21">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="10">
         <v>0.36</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>0.34</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>0.35499999999999998</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="10">
         <v>0.36</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="10">
         <v>0.34</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="10">
         <v>0.35499999999999998</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="10">
         <v>0.36</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="10">
         <v>0.35</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="10">
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+    <row r="14" spans="1:21">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <v>0.34</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <v>0.33</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <v>0.34</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="10">
         <v>0.34</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <v>0.33</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="10">
         <v>0.34</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="10">
         <v>0.34</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="10">
         <v>0.33</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="10">
         <v>0.34</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+    <row r="15" spans="1:21">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <v>0.34</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <v>0.33</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="10">
         <v>0.34</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="10">
         <v>0.33</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="10">
         <v>0.34</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="10">
         <v>0.33</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="10">
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+    <row r="16" spans="1:21">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <v>0.33</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <v>0.33</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="10">
         <v>0.33</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="10">
         <v>0.33</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="10">
         <v>0.33</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    <row r="17" spans="1:13">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <v>0.33</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <v>0.33</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
         <v>0.33</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="10">
         <v>0.33</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="10">
         <v>0.33</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    <row r="18" spans="1:13">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <v>0.33</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <v>0.33</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="10">
         <v>0.33</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="10">
         <v>0.33</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="10">
         <v>0.33</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:13">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>0.33</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <v>0.33</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="10">
         <v>0.33</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="10">
         <v>0.33500000000000002</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="10">
         <v>0.33</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="10">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    <row r="20" spans="1:13">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <v>0.33</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <v>0.32500000000000001</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <v>0.33</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="10">
         <v>0.33</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <v>0.32500000000000001</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="10">
         <v>0.33</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="10">
         <v>0.33</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="10">
         <v>0.32500000000000001</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="10">
         <v>0.33</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:13">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <v>0.31</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <v>0.3</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <v>0.30499999999999999</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="10">
         <v>0.32500000000000001</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="10">
         <v>0.315</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="10">
         <v>0.32</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="10">
         <v>0.32</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="10">
         <v>0.31</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="10">
         <v>0.315</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+    <row r="22" spans="1:13">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <v>0.29499999999999998</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="10">
         <v>0.31</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="10">
         <v>0.3</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="10">
         <v>0.30499999999999999</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="10">
         <v>0.3</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="10">
         <v>0.29499999999999998</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="10">
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:13">
+      <c r="A23" s="7">
         <v>46197</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>46197</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <v>0.29499999999999998</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="10">
         <v>0.30499999999999999</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="10">
         <v>0.29499999999999998</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="10">
         <v>0.3</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="10">
         <v>0.3</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="10">
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:13">
+      <c r="A24" s="7">
         <v>46204</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>46204</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="10">
         <v>0.27</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="10">
         <v>0.27</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="10">
         <v>0.27</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="10">
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:13">
+      <c r="A25" s="7">
         <v>46211</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>46211</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="10">
         <v>0.27</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="10">
         <v>0.26</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="10">
         <v>0.27</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="10">
         <v>0.27</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="10">
         <v>0.26</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="10">
         <v>0.27</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="10">
         <v>0.27</v>
       </c>
-      <c r="L25" s="13">
+      <c r="L25" s="10">
         <v>0.26</v>
       </c>
-      <c r="M25" s="13">
+      <c r="M25" s="10">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J26" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0.26500000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10926,845 +11142,877 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="13"/>
-    <col min="22" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="10"/>
+    <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="8" t="s">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>0.82</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <v>0.78</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>0.79</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="5">
         <v>0.75</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <v>0.71</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="5">
         <v>0.72</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="5">
         <v>0.85</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="5">
         <v>0.78</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="5">
         <v>0.79</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="5">
         <v>0.82</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>0.7</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="5">
         <v>0.76</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="10">
         <v>0.85</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="10">
         <v>0.78</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>0.79</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="10">
         <v>0.82</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="10">
         <v>0.7</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="6" spans="1:21">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
         <v>0.85</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>0.78</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>0.79</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="10">
         <v>0.82</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="10">
         <v>0.7</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+    <row r="7" spans="1:21">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="10">
         <v>0.85</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>0.78</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <v>0.79</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="10">
         <v>0.82</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="10">
         <v>0.7</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+    <row r="8" spans="1:21">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>0.85</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>0.78</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <v>0.79</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <v>0.82</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="10">
         <v>0.7</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+    <row r="9" spans="1:21">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="10">
         <v>0.85</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="10">
         <v>0.78</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="10">
         <v>0.79</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="10">
         <v>0.82</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="10">
         <v>0.7</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+    <row r="10" spans="1:21">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="10">
         <v>0.85</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>0.78</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <v>0.79</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="10">
         <v>0.82</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="10">
         <v>0.7</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:21">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>0.85</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>0.78</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <v>0.79</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="10">
         <v>0.82</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="10">
         <v>0.7</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:21">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="10">
         <v>0.85</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>0.78</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>0.79</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="10">
         <v>0.82</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="10">
         <v>0.7</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+    <row r="13" spans="1:21">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="10">
         <v>0.85</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>0.78</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>0.79</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="10">
         <v>0.82</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="10">
         <v>0.7</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+    <row r="14" spans="1:21">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <v>0.85</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <v>0.78</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <v>0.79</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="10">
         <v>0.82</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <v>0.7</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+    <row r="15" spans="1:21">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <v>0.85</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <v>0.78</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <v>0.79</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="10">
         <v>0.82</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="10">
         <v>0.7</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+    <row r="16" spans="1:21">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <v>0.8</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <v>0.75</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <v>0.78</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="10">
         <v>0.8</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="10">
         <v>0.75</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    <row r="17" spans="1:10">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <v>0.8</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <v>0.75</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <v>0.78</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="10">
         <v>0.8</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
         <v>0.75</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    <row r="18" spans="1:10">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <v>0.8</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <v>0.75</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <v>0.78</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="10">
         <v>0.8</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="10">
         <v>0.75</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:10">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <v>0.8</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>0.75</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <v>0.78</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="10">
         <v>0.8</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="10">
         <v>0.75</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    <row r="20" spans="1:10">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <v>0.78</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <v>0.72</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <v>0.75</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="10">
         <v>0.8</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <v>0.75</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:10">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <v>0.75</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <v>0.72</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <v>0.74</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="10">
         <v>0.8</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="10">
         <v>0.75</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+    <row r="22" spans="1:10">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <v>0.75</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <v>0.7</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <v>0.74</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="10">
         <v>0.8</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="10">
         <v>0.75</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:10">
+      <c r="A23" s="7">
         <v>46197</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>46197</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <v>0.74</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <v>0.71</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <v>0.73</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="10">
         <v>0.8</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="10">
         <v>0.75</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:10">
+      <c r="A24" s="7">
         <v>46204</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>46204</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="10">
         <v>0.73</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="10">
         <v>0.69</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="10">
         <v>0.71</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="10">
         <v>0.8</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="10">
         <v>0.75</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="10">
         <v>0.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:10">
+      <c r="A25" s="7">
         <v>46211</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>46211</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="10">
         <v>0.69</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="10">
         <v>0.66</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="10">
         <v>0.69</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="10">
         <v>0.8</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="10">
         <v>0.75</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="10">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0.69</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0.66</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0.69</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="J26" s="10">
         <v>0.76</v>
       </c>
     </row>
@@ -11782,1060 +12030,1101 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="17" customWidth="1"/>
-    <col min="6" max="13" width="9" style="17"/>
-    <col min="14" max="21" width="9" style="13"/>
-    <col min="22" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="14" customWidth="1"/>
+    <col min="6" max="13" width="9" style="14"/>
+    <col min="14" max="21" width="9" style="10"/>
+    <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="15" t="s">
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="7">
         <v>46043</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46043</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="12">
         <v>12</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="12">
         <v>11</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="12">
         <v>11.5</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="12">
         <v>19</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="12">
         <v>18</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="12">
         <v>18.5</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="12">
         <v>10</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="12">
         <v>9</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="12">
         <v>9.5</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="7">
         <v>46050</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>46050</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="12">
         <v>12</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="12">
         <v>11</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="12">
         <v>11.5</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="12">
         <v>19</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="12">
         <v>18</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="12">
         <v>18.5</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="12">
         <v>10</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="12">
         <v>9</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="12">
         <v>9.5</v>
       </c>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="7">
         <v>46057</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>46057</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>12</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="14">
         <v>11</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="14">
         <v>11.5</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="14">
         <v>19</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="14">
         <v>18</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="14">
         <v>18.5</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="14">
         <v>10</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="14">
         <v>9</v>
       </c>
-      <c r="M5" s="17">
+      <c r="M5" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+    <row r="6" spans="1:21">
+      <c r="A6" s="7">
         <v>46064</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>46064</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="14">
         <v>12</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="14">
         <v>11</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>11.5</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>19</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="14">
         <v>18</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="14">
         <v>18.5</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="14">
         <v>10</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="14">
         <v>9</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+    <row r="7" spans="1:21">
+      <c r="A7" s="7">
         <v>46078</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>46078</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>12</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="14">
         <v>11</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="14">
         <v>11.5</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="14">
         <v>19</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="14">
         <v>18</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="14">
         <v>18.5</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="14">
         <v>10</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="14">
         <v>9</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+    <row r="8" spans="1:21">
+      <c r="A8" s="7">
         <v>46085</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>46085</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="14">
         <v>12</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="14">
         <v>11</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="14">
         <v>11.5</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="14">
         <v>19</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="14">
         <v>18</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="14">
         <v>18.5</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="14">
         <v>10</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="14">
         <v>9</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+    <row r="9" spans="1:21">
+      <c r="A9" s="7">
         <v>46092</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>46092</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>12</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="14">
         <v>11</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="14">
         <v>11.5</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="14">
         <v>19</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="14">
         <v>18</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="14">
         <v>18.5</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="14">
         <v>10</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="14">
         <v>9</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+    <row r="10" spans="1:21">
+      <c r="A10" s="7">
         <v>46099</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>46099</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="14">
         <v>12</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="14">
         <v>11</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="14">
         <v>11.5</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="14">
         <v>19</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="14">
         <v>18</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="14">
         <v>18.5</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="14">
         <v>10</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="14">
         <v>9</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:21">
+      <c r="A11" s="7">
         <v>46106</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>46106</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>12</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="14">
         <v>11</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="14">
         <v>11.5</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="14">
         <v>19</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="14">
         <v>18</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="14">
         <v>18.5</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="14">
         <v>10</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="14">
         <v>9</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:21">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>46113</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="14">
         <v>12</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="14">
         <v>11</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="14">
         <v>11.5</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="14">
         <v>19</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="14">
         <v>18</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="14">
         <v>18.5</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="14">
         <v>10</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="14">
         <v>9</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="14">
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+    <row r="13" spans="1:21">
+      <c r="A13" s="7">
         <v>46120</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>46120</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="14">
         <v>11.5</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="14">
         <v>10.5</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="14">
         <v>11</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="14">
         <v>18.5</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <v>17.5</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="14">
         <v>18</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="14">
         <v>9.5</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="14">
         <v>8.5</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="14">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+    <row r="14" spans="1:21">
+      <c r="A14" s="7">
         <v>46127</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>46127</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="14">
         <v>11</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="14">
         <v>10</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="14">
         <v>10.5</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="14">
         <v>18.5</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="14">
         <v>17</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="14">
         <v>17.75</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="14">
         <v>9</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="14">
         <v>8.5</v>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+    <row r="15" spans="1:21">
+      <c r="A15" s="7">
         <v>46134</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>46134</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="14">
         <v>11</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="14">
         <v>10</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="14">
         <v>10.5</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="14">
         <v>18.5</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="14">
         <v>17</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="14">
         <v>17.75</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="14">
         <v>9</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="14">
         <v>8.5</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+    <row r="16" spans="1:21">
+      <c r="A16" s="7">
         <v>46141</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>46141</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="14">
         <v>11</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="14">
         <v>10</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="14">
         <v>10.5</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="14">
         <v>18.5</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="14">
         <v>17</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="14">
         <v>17.75</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="14">
         <v>9</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="14">
         <v>8.5</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+    <row r="17" spans="1:13">
+      <c r="A17" s="7">
         <v>46155</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>46155</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="14">
         <v>11</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="14">
         <v>10</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="14">
         <v>10.5</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="14">
         <v>18.5</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="14">
         <v>17</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="14">
         <v>17.75</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="14">
         <v>9</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="14">
         <v>8.5</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+    <row r="18" spans="1:13">
+      <c r="A18" s="7">
         <v>46164</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="14">
         <v>11</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="14">
         <v>10</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="14">
         <v>10.5</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="14">
         <v>18.5</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="14">
         <v>17</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="14">
         <v>17.75</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="14">
         <v>9</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="14">
         <v>8.5</v>
       </c>
-      <c r="M18" s="17">
+      <c r="M18" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+    <row r="19" spans="1:13">
+      <c r="A19" s="7">
         <v>46169</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>46169</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="14">
         <v>11</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="14">
         <v>10</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="14">
         <v>10.5</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="14">
         <v>18.5</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="14">
         <v>17</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="14">
         <v>17.75</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="14">
         <v>9</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="14">
         <v>8.5</v>
       </c>
-      <c r="M19" s="17">
+      <c r="M19" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+    <row r="20" spans="1:13">
+      <c r="A20" s="7">
         <v>46176</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>46176</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="14">
         <v>11</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="14">
         <v>10</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="14">
         <v>10.5</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="14">
         <v>18.5</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="14">
         <v>17</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="14">
         <v>17.75</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="14">
         <v>9</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="14">
         <v>8.5</v>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="14">
         <v>8.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="21" spans="1:13">
+      <c r="A21" s="7">
         <v>46183</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>46183</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="14">
         <v>10.5</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="14">
         <v>9.5</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="14">
         <v>10</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="14">
         <v>17</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="14">
         <v>16</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="14">
         <v>16.5</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="14">
         <v>8.5</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="14">
         <v>8</v>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+    <row r="22" spans="1:13">
+      <c r="A22" s="7">
         <v>46190</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>46190</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="14">
         <v>10.5</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="14">
         <v>9.5</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="14">
         <v>10</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="14">
         <v>17</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="14">
         <v>16</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="14">
         <v>16.5</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="14">
         <v>8.5</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="14">
         <v>8</v>
       </c>
-      <c r="M22" s="17">
+      <c r="M22" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+    <row r="23" spans="1:13">
+      <c r="A23" s="7">
         <v>46197</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>46197</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="14">
         <v>10.5</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="14">
         <v>9.5</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="14">
         <v>10</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="14">
         <v>17</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="14">
         <v>16</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="14">
         <v>16.5</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="14">
         <v>8.5</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="14">
         <v>8</v>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:13">
+      <c r="A24" s="7">
         <v>46204</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>46204</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="14">
         <v>10.5</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="14">
         <v>9.5</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="14">
         <v>10</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="14">
         <v>17</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="14">
         <v>16</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="14">
         <v>16.5</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="14">
         <v>8.5</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="14">
         <v>8</v>
       </c>
-      <c r="M24" s="17">
+      <c r="M24" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:13">
+      <c r="A25" s="7">
         <v>46211</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>46211</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="8">
         <v>0.75694444444444497</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="14">
         <v>10.5</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="14">
         <v>9.5</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="14">
         <v>10</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="14">
         <v>17</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="14">
         <v>16</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="14">
         <v>16.5</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="14">
         <v>8.5</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="14">
         <v>8</v>
       </c>
-      <c r="M25" s="17">
+      <c r="M25" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46218</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="F26" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="G26" s="14">
+        <v>10</v>
+      </c>
+      <c r="H26" s="14">
+        <v>17</v>
+      </c>
+      <c r="I26" s="14">
+        <v>16</v>
+      </c>
+      <c r="J26" s="14">
+        <v>16.5</v>
+      </c>
+      <c r="K26" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="L26" s="14">
+        <v>8</v>
+      </c>
+      <c r="M26" s="14">
         <v>8</v>
       </c>
     </row>
@@ -12854,7 +13143,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12866,18 +13155,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12885,25 +13174,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -12911,19 +13200,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -12931,19 +13220,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -12951,13 +13240,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -12965,13 +13254,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CA905C-5792-49E9-8D1E-5C5A4E22435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D80F58-2444-FA44-A89A-82D3DA5C08C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27980" yWindow="780" windowWidth="23020" windowHeight="24960" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -476,6 +476,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -555,6 +558,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -674,6 +680,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -753,6 +762,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -872,6 +884,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -951,6 +966,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1070,6 +1088,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1149,6 +1170,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1490,6 +1514,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1570,6 +1597,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1688,6 +1718,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1768,6 +1801,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.1299999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1886,6 +1922,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1966,6 +2005,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2307,6 +2349,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2463,6 +2508,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2619,6 +2667,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2699,6 +2750,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.26500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3041,6 +3095,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3121,6 +3178,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3239,6 +3299,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3319,6 +3382,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3659,6 +3725,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3738,6 +3807,9 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -3857,6 +3929,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3936,6 +4011,9 @@
                   <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4055,6 +4133,9 @@
                 <c:pt idx="23">
                   <c:v>46218</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46225</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4134,6 +4215,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -7587,13 +7671,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="13"/>
     <col min="15" max="16" width="9" style="14"/>
     <col min="17" max="21" width="9" style="10"/>
@@ -8904,6 +8988,56 @@
         <v>13.1</v>
       </c>
       <c r="P26" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="13">
+        <v>34</v>
+      </c>
+      <c r="F27" s="13">
+        <v>33</v>
+      </c>
+      <c r="G27" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H27" s="13">
+        <v>33</v>
+      </c>
+      <c r="I27" s="13">
+        <v>32</v>
+      </c>
+      <c r="J27" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K27" s="13">
+        <v>32</v>
+      </c>
+      <c r="L27" s="13">
+        <v>30</v>
+      </c>
+      <c r="M27" s="13">
+        <v>31</v>
+      </c>
+      <c r="N27" s="13">
+        <v>22</v>
+      </c>
+      <c r="O27" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P27" s="14">
         <v>17.5</v>
       </c>
     </row>
@@ -8922,13 +9056,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
@@ -10016,6 +10150,47 @@
       </c>
       <c r="M26" s="10">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="F27" s="10">
+        <v>0.83</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0.84</v>
+      </c>
+      <c r="H27" s="10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J27" s="10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.93</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -10032,13 +10207,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
@@ -11126,6 +11301,47 @@
       </c>
       <c r="M26" s="10">
         <v>0.26500000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="F27" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="I27" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -11142,12 +11358,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
@@ -12014,6 +12230,38 @@
       </c>
       <c r="J26" s="10">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.69</v>
+      </c>
+      <c r="F27" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0.68</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I27" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -12030,12 +12278,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:U27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="14" customWidth="1"/>
     <col min="6" max="13" width="9" style="14"/>
@@ -13125,6 +13373,47 @@
         <v>8</v>
       </c>
       <c r="M26" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46225</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="F27" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="G27" s="14">
+        <v>10</v>
+      </c>
+      <c r="H27" s="14">
+        <v>17</v>
+      </c>
+      <c r="I27" s="14">
+        <v>16</v>
+      </c>
+      <c r="J27" s="14">
+        <v>16.5</v>
+      </c>
+      <c r="K27" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="L27" s="14">
+        <v>8</v>
+      </c>
+      <c r="M27" s="14">
         <v>8</v>
       </c>
     </row>
@@ -13143,7 +13432,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13155,9 +13444,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D80F58-2444-FA44-A89A-82D3DA5C08C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27980" yWindow="780" windowWidth="23020" windowHeight="24960" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -204,24 +204,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +234,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -284,7 +284,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -300,32 +300,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -333,8 +333,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,7 +352,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -486,7 +486,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -690,7 +690,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -894,7 +894,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$1112</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -1271,7 +1271,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1390,7 +1390,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2225,7 +2225,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2971,7 +2971,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3601,7 +3601,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7672,19 +7672,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="13"/>
     <col min="15" max="16" width="9" style="14"/>
     <col min="17" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -7781,7 +7781,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -7836,7 +7836,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -7891,7 +7891,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -8241,7 +8241,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -9057,17 +9057,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -9111,7 +9111,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9152,7 +9152,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -9201,7 +9201,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -9250,7 +9250,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -9455,7 +9455,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -9619,7 +9619,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -10152,7 +10152,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -10208,17 +10208,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -10262,7 +10262,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -10303,7 +10303,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -10352,7 +10352,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -10401,7 +10401,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -10524,7 +10524,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -10647,7 +10647,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -10729,7 +10729,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -11057,7 +11057,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -11098,7 +11098,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -11139,7 +11139,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -11221,7 +11221,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -11303,7 +11303,7 @@
         <v>0.26500000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -11359,17 +11359,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -11407,7 +11407,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11442,7 +11442,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -11485,7 +11485,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -11528,7 +11528,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -12136,7 +12136,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -12200,7 +12200,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -12279,11 +12279,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="14" customWidth="1"/>
     <col min="6" max="13" width="9" style="14"/>
@@ -12291,7 +12291,7 @@
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -12335,7 +12335,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12376,7 +12376,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -12425,7 +12425,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -12474,7 +12474,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -12556,7 +12556,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -12597,7 +12597,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -12638,7 +12638,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -12925,7 +12925,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -12966,7 +12966,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -13007,7 +13007,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -13130,7 +13130,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -13432,7 +13432,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13444,18 +13444,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13463,25 +13463,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -13489,19 +13489,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -13509,19 +13509,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -13529,13 +13529,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -13543,13 +13543,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D80F58-2444-FA44-A89A-82D3DA5C08C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC0B152-9198-411B-AA24-BE5AB81933EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -479,6 +479,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -683,6 +686,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -887,6 +893,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1090,6 +1099,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>46225</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7671,7 +7683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9039,6 +9051,20 @@
       </c>
       <c r="P27" s="14">
         <v>17.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC0B152-9198-411B-AA24-BE5AB81933EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F24A9B-7AD6-4570-9A8E-C0CB4519C028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -566,6 +566,9 @@
                 <c:pt idx="24">
                   <c:v>33.5</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>33.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -773,6 +776,9 @@
                 <c:pt idx="24">
                   <c:v>32.5</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>32.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -980,6 +986,9 @@
                 <c:pt idx="24">
                   <c:v>31</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>31</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1185,6 +1194,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1246,7 +1258,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -1306,7 +1318,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -1341,14 +1353,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -1384,7 +1396,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -1529,6 +1541,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1612,6 +1627,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1733,6 +1751,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1816,6 +1837,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.1100000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1937,6 +1961,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2020,6 +2047,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.91</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2080,7 +2110,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2141,7 +2171,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2176,14 +2206,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -2219,7 +2249,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -2364,6 +2394,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2523,6 +2556,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2682,6 +2718,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2764,6 +2803,9 @@
                   <c:v>0.26500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -2825,7 +2867,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2886,7 +2928,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -2929,7 +2971,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -2965,7 +3007,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -3110,6 +3152,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3193,6 +3238,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3314,6 +3362,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3396,6 +3447,9 @@
                   <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3457,7 +3511,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -3517,7 +3571,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -3552,14 +3606,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -3595,7 +3649,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -3740,6 +3794,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3822,6 +3879,9 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -3944,6 +4004,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4026,6 +4089,9 @@
                   <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4148,6 +4214,9 @@
                 <c:pt idx="24">
                   <c:v>46225</c:v>
                 </c:pt>
+                <c:pt idx="25">
+                  <c:v>46232</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4230,6 +4299,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -4291,7 +4363,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -4352,7 +4424,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -4394,7 +4466,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -4430,7 +4502,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -9066,6 +9138,42 @@
       <c r="D28" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E28" s="13">
+        <v>34</v>
+      </c>
+      <c r="F28" s="13">
+        <v>33</v>
+      </c>
+      <c r="G28" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H28" s="13">
+        <v>33</v>
+      </c>
+      <c r="I28" s="13">
+        <v>32</v>
+      </c>
+      <c r="J28" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K28" s="13">
+        <v>32</v>
+      </c>
+      <c r="L28" s="13">
+        <v>30</v>
+      </c>
+      <c r="M28" s="13">
+        <v>31</v>
+      </c>
+      <c r="N28" s="13">
+        <v>22</v>
+      </c>
+      <c r="O28" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P28" s="14">
+        <v>17.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9082,7 +9190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
@@ -10217,6 +10325,47 @@
       </c>
       <c r="M27" s="10">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="F28" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0.81</v>
+      </c>
+      <c r="H28" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I28" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J28" s="10">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="L28" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -10233,13 +10382,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
@@ -11367,6 +11516,47 @@
         <v>0.26</v>
       </c>
       <c r="M27" s="10">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="F28" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="I28" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="J28" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="L28" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="M28" s="10">
         <v>0.26</v>
       </c>
     </row>
@@ -11384,7 +11574,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -12287,6 +12477,38 @@
         <v>0.7</v>
       </c>
       <c r="J27" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.68</v>
+      </c>
+      <c r="F28" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I28" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J28" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -12304,7 +12526,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -13440,6 +13662,47 @@
         <v>8</v>
       </c>
       <c r="M27" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46232</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="F28" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="G28" s="14">
+        <v>10</v>
+      </c>
+      <c r="H28" s="14">
+        <v>17</v>
+      </c>
+      <c r="I28" s="14">
+        <v>16</v>
+      </c>
+      <c r="J28" s="14">
+        <v>16.5</v>
+      </c>
+      <c r="K28" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="L28" s="14">
+        <v>8</v>
+      </c>
+      <c r="M28" s="14">
         <v>8</v>
       </c>
     </row>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F24A9B-7AD6-4570-9A8E-C0CB4519C028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A82F039-755A-4016-B50F-342BCDB4F773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A82F039-755A-4016-B50F-342BCDB4F773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883829C4-C88C-425F-AA8B-B9870C42B6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -482,6 +482,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -692,6 +695,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -902,6 +908,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1111,6 +1120,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1544,6 +1556,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1754,6 +1769,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1963,6 +1981,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2397,6 +2418,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2559,6 +2583,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2720,6 +2747,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3155,6 +3185,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3364,6 +3397,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3797,6 +3833,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4007,6 +4046,9 @@
                 <c:pt idx="25">
                   <c:v>46232</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4216,6 +4258,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46239</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7755,7 +7800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9175,6 +9220,20 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9190,7 +9249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
@@ -10366,6 +10425,20 @@
       </c>
       <c r="M28" s="10">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -10382,7 +10455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
@@ -11558,6 +11631,20 @@
       </c>
       <c r="M28" s="10">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -11574,7 +11661,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -12510,6 +12597,20 @@
       </c>
       <c r="J28" s="10">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -12526,7 +12627,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -13704,6 +13805,20 @@
       </c>
       <c r="M28" s="14">
         <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46239</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883829C4-C88C-425F-AA8B-B9870C42B6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD72721-7A1C-400C-84C9-8F96DE921ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -572,6 +572,9 @@
                 <c:pt idx="25">
                   <c:v>33.5</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>33.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -785,6 +788,9 @@
                 <c:pt idx="25">
                   <c:v>32.5</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>32.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -998,6 +1004,9 @@
                 <c:pt idx="25">
                   <c:v>31</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>31</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1209,6 +1218,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1646,6 +1658,9 @@
                 <c:pt idx="25">
                   <c:v>0.81</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.8</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1859,6 +1874,9 @@
                 <c:pt idx="25">
                   <c:v>1.1100000000000001</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2071,6 +2089,9 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2836,6 +2857,9 @@
                   <c:v>0.26</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>0.26</c:v>
                 </c:pt>
               </c:numCache>
@@ -3275,6 +3299,9 @@
                 <c:pt idx="25">
                   <c:v>0.67</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.67</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3486,6 +3513,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3923,6 +3953,9 @@
                 <c:pt idx="25">
                   <c:v>10</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4136,6 +4169,9 @@
                 <c:pt idx="25">
                   <c:v>16.5</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>16.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4347,6 +4383,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -9233,6 +9272,42 @@
       <c r="D29" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E29" s="13">
+        <v>34</v>
+      </c>
+      <c r="F29" s="13">
+        <v>33</v>
+      </c>
+      <c r="G29" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H29" s="13">
+        <v>33</v>
+      </c>
+      <c r="I29" s="13">
+        <v>32</v>
+      </c>
+      <c r="J29" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K29" s="13">
+        <v>32</v>
+      </c>
+      <c r="L29" s="13">
+        <v>30</v>
+      </c>
+      <c r="M29" s="13">
+        <v>31</v>
+      </c>
+      <c r="N29" s="13">
+        <v>22</v>
+      </c>
+      <c r="O29" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P29" s="14">
+        <v>17.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10440,6 +10515,33 @@
       <c r="D29" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E29" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="F29" s="10">
+        <v>0.78</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="H29" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I29" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="J29" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="L29" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0.9</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11646,6 +11748,33 @@
       <c r="D29" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="E29" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="F29" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="J29" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="L29" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0.26</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12611,6 +12740,24 @@
       </c>
       <c r="D29" s="9" t="s">
         <v>40</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.68</v>
+      </c>
+      <c r="F29" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J29" s="10">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -13819,6 +13966,33 @@
       </c>
       <c r="D29" s="9" t="s">
         <v>40</v>
+      </c>
+      <c r="E29" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="F29" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="G29" s="14">
+        <v>10</v>
+      </c>
+      <c r="H29" s="14">
+        <v>17</v>
+      </c>
+      <c r="I29" s="14">
+        <v>16</v>
+      </c>
+      <c r="J29" s="14">
+        <v>16.5</v>
+      </c>
+      <c r="K29" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="L29" s="14">
+        <v>8</v>
+      </c>
+      <c r="M29" s="14">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD72721-7A1C-400C-84C9-8F96DE921ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315E7E5D-7B50-4FEB-B757-1CE5F23D8B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -485,6 +485,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -573,6 +576,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -701,6 +707,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -789,6 +798,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -917,6 +929,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1005,6 +1020,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1133,6 +1151,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1221,6 +1242,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1571,6 +1595,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1659,6 +1686,9 @@
                   <c:v>0.81</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>0.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -1787,6 +1817,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1875,6 +1908,9 @@
                   <c:v>1.1100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>1.1000000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -2003,6 +2039,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2091,6 +2130,9 @@
                   <c:v>0.91</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>0.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -2442,6 +2484,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2607,6 +2652,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2772,6 +2820,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2861,6 +2912,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.28000000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3212,6 +3266,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3302,10 +3359,13 @@
                 <c:pt idx="26">
                   <c:v>0.67</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.68</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-4748-4EC9-A6AC-E57B807BE2B9}"/>
@@ -3428,6 +3488,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3518,10 +3581,13 @@
                 <c:pt idx="26">
                   <c:v>0.7</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-4748-4EC9-A6AC-E57B807BE2B9}"/>
@@ -3866,6 +3932,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3955,6 +4024,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4082,6 +4154,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4171,6 +4246,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4298,6 +4376,9 @@
                 <c:pt idx="26">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="27">
+                  <c:v>46246</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4387,6 +4468,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7839,7 +7923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9309,6 +9393,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="13">
+        <v>34</v>
+      </c>
+      <c r="F30" s="13">
+        <v>33</v>
+      </c>
+      <c r="G30" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H30" s="13">
+        <v>33</v>
+      </c>
+      <c r="I30" s="13">
+        <v>32</v>
+      </c>
+      <c r="J30" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K30" s="13">
+        <v>32</v>
+      </c>
+      <c r="L30" s="13">
+        <v>30</v>
+      </c>
+      <c r="M30" s="13">
+        <v>31</v>
+      </c>
+      <c r="N30" s="13">
+        <v>22</v>
+      </c>
+      <c r="O30" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P30" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9324,7 +9458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
@@ -10540,6 +10674,47 @@
         <v>0.88</v>
       </c>
       <c r="M29" s="10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0.78</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="H30" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="I30" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="J30" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K30" s="10">
+        <v>1</v>
+      </c>
+      <c r="L30" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="M30" s="10">
         <v>0.9</v>
       </c>
     </row>
@@ -10557,7 +10732,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
@@ -11774,6 +11949,47 @@
       </c>
       <c r="M29" s="10">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="I30" s="10">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="J30" s="10">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="K30" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="L30" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0.28000000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -11790,7 +12006,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -12757,6 +12973,38 @@
         <v>0.7</v>
       </c>
       <c r="J29" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.69</v>
+      </c>
+      <c r="F30" s="10">
+        <v>0.66</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0.68</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I30" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J30" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -12774,7 +13022,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -13993,6 +14241,47 @@
       </c>
       <c r="M29" s="14">
         <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="14">
+        <v>11</v>
+      </c>
+      <c r="F30" s="14">
+        <v>10</v>
+      </c>
+      <c r="G30" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>18</v>
+      </c>
+      <c r="I30" s="14">
+        <v>17</v>
+      </c>
+      <c r="J30" s="14">
+        <v>17</v>
+      </c>
+      <c r="K30" s="14">
+        <v>9</v>
+      </c>
+      <c r="L30" s="14">
+        <v>8</v>
+      </c>
+      <c r="M30" s="14">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315E7E5D-7B50-4FEB-B757-1CE5F23D8B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63293397-32CA-4482-843F-6CDE19705063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -488,6 +488,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -579,6 +582,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -710,6 +716,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -801,6 +810,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -932,6 +944,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1023,6 +1038,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1154,6 +1172,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1245,6 +1266,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1598,6 +1622,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1690,6 +1717,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.1200000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1820,6 +1850,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1912,6 +1945,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2042,6 +2078,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2134,6 +2173,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.1499999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2487,6 +2529,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2655,6 +2700,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2823,6 +2871,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2915,6 +2966,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3269,6 +3323,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3361,6 +3418,9 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3491,6 +3551,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3582,6 +3645,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3935,6 +4001,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4026,6 +4095,9 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4157,6 +4229,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4248,6 +4323,9 @@
                   <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -4379,6 +4457,9 @@
                 <c:pt idx="27">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="28">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4470,6 +4551,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -7923,7 +8007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9443,6 +9527,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="13">
+        <v>34</v>
+      </c>
+      <c r="F31" s="13">
+        <v>33</v>
+      </c>
+      <c r="G31" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H31" s="13">
+        <v>33</v>
+      </c>
+      <c r="I31" s="13">
+        <v>32</v>
+      </c>
+      <c r="J31" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K31" s="13">
+        <v>32</v>
+      </c>
+      <c r="L31" s="13">
+        <v>30</v>
+      </c>
+      <c r="M31" s="13">
+        <v>31</v>
+      </c>
+      <c r="N31" s="13">
+        <v>22</v>
+      </c>
+      <c r="O31" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P31" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9458,7 +9592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
@@ -10716,6 +10850,47 @@
       </c>
       <c r="M30" s="10">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F31" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G31" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H31" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="I31" s="10">
+        <v>1.23</v>
+      </c>
+      <c r="J31" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="K31" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L31" s="10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="M31" s="10">
+        <v>1.1499999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10732,7 +10907,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
@@ -11990,6 +12165,47 @@
       </c>
       <c r="M30" s="10">
         <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="F31" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="I31" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="J31" s="10">
+        <v>0.34</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="L31" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="M31" s="10">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -12006,7 +12222,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -13005,6 +13221,38 @@
         <v>0.7</v>
       </c>
       <c r="J30" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F31" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I31" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J31" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -13022,7 +13270,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
@@ -14281,6 +14529,47 @@
         <v>8</v>
       </c>
       <c r="M30" s="14">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46253</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="14">
+        <v>11</v>
+      </c>
+      <c r="F31" s="14">
+        <v>10</v>
+      </c>
+      <c r="G31" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>18</v>
+      </c>
+      <c r="I31" s="14">
+        <v>17</v>
+      </c>
+      <c r="J31" s="14">
+        <v>17</v>
+      </c>
+      <c r="K31" s="14">
+        <v>9</v>
+      </c>
+      <c r="L31" s="14">
+        <v>8</v>
+      </c>
+      <c r="M31" s="14">
         <v>8.5</v>
       </c>
     </row>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63293397-32CA-4482-843F-6CDE19705063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45BA455-3EE6-B649-B252-2E279B61BA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -204,24 +204,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +234,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -284,7 +284,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -300,32 +300,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -333,8 +333,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,7 +352,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -491,6 +491,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -498,7 +501,7 @@
             <c:numRef>
               <c:f>Polysilicon!$G$3:$G$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>53</c:v>
@@ -585,6 +588,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -719,6 +725,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -726,7 +735,7 @@
             <c:numRef>
               <c:f>Polysilicon!$J$3:$J$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>52</c:v>
@@ -813,6 +822,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -947,6 +959,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -954,7 +969,7 @@
             <c:numRef>
               <c:f>Polysilicon!$M$3:$M$1112</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="1110"/>
                 <c:pt idx="0">
                   <c:v>50</c:v>
@@ -1041,6 +1056,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1175,6 +1193,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1269,6 +1290,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1367,7 +1391,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1486,7 +1510,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1625,6 +1649,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1719,6 +1746,9 @@
                   <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>1.1200000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1853,6 +1883,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1947,6 +1980,9 @@
                   <c:v>1.1000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>1.25</c:v>
                 </c:pt>
               </c:numCache>
@@ -2081,6 +2117,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2175,6 +2214,9 @@
                   <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>1.1499999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -2393,7 +2435,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2532,6 +2574,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2703,6 +2748,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2874,6 +2922,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2969,6 +3020,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3187,7 +3241,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3326,6 +3380,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3420,6 +3477,9 @@
                   <c:v>0.68</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3554,6 +3614,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3648,6 +3711,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3865,7 +3931,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4004,6 +4070,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4098,6 +4167,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4232,6 +4304,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4326,6 +4401,9 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -4460,6 +4538,9 @@
                 <c:pt idx="28">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="29">
+                  <c:v>46260</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4554,6 +4635,9 @@
                   <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -8007,20 +8091,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="9" style="13"/>
     <col min="15" max="16" width="9" style="14"/>
     <col min="17" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="4" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -8070,7 +8154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -8117,7 +8201,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -8172,7 +8256,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -8227,7 +8311,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -8277,7 +8361,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -8327,7 +8411,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -8377,7 +8461,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -8427,7 +8511,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -8477,7 +8561,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -8527,7 +8611,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -8577,7 +8661,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -8627,7 +8711,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -8677,7 +8761,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -8727,7 +8811,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -8777,7 +8861,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -8827,7 +8911,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -8877,7 +8961,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -8927,7 +9011,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -8977,7 +9061,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -9027,7 +9111,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -9077,7 +9161,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -9127,7 +9211,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -9177,7 +9261,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -9227,7 +9311,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -9277,7 +9361,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -9327,7 +9411,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -9377,7 +9461,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" s="7">
         <v>46232</v>
       </c>
@@ -9427,7 +9511,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" s="7">
         <v>46239</v>
       </c>
@@ -9477,7 +9561,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="A30" s="7">
         <v>46246</v>
       </c>
@@ -9527,7 +9611,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="A31" s="7">
         <v>46253</v>
       </c>
@@ -9574,6 +9658,56 @@
         <v>13.1</v>
       </c>
       <c r="P31" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="13">
+        <v>45</v>
+      </c>
+      <c r="F32" s="13">
+        <v>33</v>
+      </c>
+      <c r="G32" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H32" s="13">
+        <v>43</v>
+      </c>
+      <c r="I32" s="13">
+        <v>32</v>
+      </c>
+      <c r="J32" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K32" s="13">
+        <v>41</v>
+      </c>
+      <c r="L32" s="13">
+        <v>30</v>
+      </c>
+      <c r="M32" s="13">
+        <v>31</v>
+      </c>
+      <c r="N32" s="13">
+        <v>22</v>
+      </c>
+      <c r="O32" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P32" s="14">
         <v>17.5</v>
       </c>
     </row>
@@ -9592,18 +9726,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="4" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -9647,7 +9781,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9688,7 +9822,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -9737,7 +9871,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -9786,7 +9920,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -9827,7 +9961,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -9868,7 +10002,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -9909,7 +10043,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -9950,7 +10084,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -9991,7 +10125,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -10032,7 +10166,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -10073,7 +10207,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -10114,7 +10248,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -10155,7 +10289,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -10196,7 +10330,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -10237,7 +10371,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -10278,7 +10412,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -10319,7 +10453,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -10360,7 +10494,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -10401,7 +10535,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -10442,7 +10576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -10483,7 +10617,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -10524,7 +10658,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -10565,7 +10699,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -10606,7 +10740,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -10647,7 +10781,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -10688,7 +10822,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -10729,7 +10863,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="7">
         <v>46232</v>
       </c>
@@ -10770,7 +10904,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="7">
         <v>46239</v>
       </c>
@@ -10811,7 +10945,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="7">
         <v>46246</v>
       </c>
@@ -10852,7 +10986,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="7">
         <v>46253</v>
       </c>
@@ -10890,6 +11024,47 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="M31" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F32" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H32" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="I32" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="J32" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="K32" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L32" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M32" s="10">
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -10907,18 +11082,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="4" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -10962,7 +11137,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11003,7 +11178,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -11052,7 +11227,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -11101,7 +11276,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -11142,7 +11317,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -11183,7 +11358,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -11224,7 +11399,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -11265,7 +11440,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -11306,7 +11481,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -11347,7 +11522,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -11388,7 +11563,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -11429,7 +11604,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -11470,7 +11645,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -11511,7 +11686,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -11552,7 +11727,7 @@
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -11593,7 +11768,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -11634,7 +11809,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -11675,7 +11850,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -11716,7 +11891,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -11757,7 +11932,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -11798,7 +11973,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -11839,7 +12014,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -11880,7 +12055,7 @@
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -11921,7 +12096,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -11962,7 +12137,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -12003,7 +12178,7 @@
         <v>0.26500000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -12044,7 +12219,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="7">
         <v>46232</v>
       </c>
@@ -12085,7 +12260,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="7">
         <v>46239</v>
       </c>
@@ -12126,7 +12301,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="7">
         <v>46246</v>
       </c>
@@ -12167,7 +12342,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="7">
         <v>46253</v>
       </c>
@@ -12206,6 +12381,47 @@
       </c>
       <c r="M31" s="10">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="F32" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -12222,18 +12438,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="10"/>
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="4" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -12271,7 +12487,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12306,7 +12522,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -12349,7 +12565,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -12392,7 +12608,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -12424,7 +12640,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -12456,7 +12672,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -12488,7 +12704,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -12520,7 +12736,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -12552,7 +12768,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -12584,7 +12800,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -12616,7 +12832,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -12648,7 +12864,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -12680,7 +12896,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -12712,7 +12928,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -12744,7 +12960,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -12776,7 +12992,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -12808,7 +13024,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -12840,7 +13056,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -12872,7 +13088,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -12904,7 +13120,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -12936,7 +13152,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -12968,7 +13184,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -13000,7 +13216,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -13032,7 +13248,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -13064,7 +13280,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -13096,7 +13312,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -13128,7 +13344,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="7">
         <v>46232</v>
       </c>
@@ -13160,7 +13376,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="7">
         <v>46239</v>
       </c>
@@ -13192,7 +13408,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="7">
         <v>46246</v>
       </c>
@@ -13224,7 +13440,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="7">
         <v>46253</v>
       </c>
@@ -13253,6 +13469,38 @@
         <v>0.7</v>
       </c>
       <c r="J31" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F32" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J32" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -13270,12 +13518,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="14" customWidth="1"/>
     <col min="6" max="13" width="9" style="14"/>
@@ -13283,7 +13531,7 @@
     <col min="22" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="4" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>21</v>
       </c>
@@ -13327,7 +13575,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -13368,7 +13616,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" s="7">
         <v>46043</v>
       </c>
@@ -13417,7 +13665,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" s="7">
         <v>46050</v>
       </c>
@@ -13466,7 +13714,7 @@
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" s="7">
         <v>46057</v>
       </c>
@@ -13507,7 +13755,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" s="7">
         <v>46064</v>
       </c>
@@ -13548,7 +13796,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" s="7">
         <v>46078</v>
       </c>
@@ -13589,7 +13837,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" s="7">
         <v>46085</v>
       </c>
@@ -13630,7 +13878,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="A9" s="7">
         <v>46092</v>
       </c>
@@ -13671,7 +13919,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="A10" s="7">
         <v>46099</v>
       </c>
@@ -13712,7 +13960,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="A11" s="7">
         <v>46106</v>
       </c>
@@ -13753,7 +14001,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="A12" s="7">
         <v>46113</v>
       </c>
@@ -13794,7 +14042,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="A13" s="7">
         <v>46120</v>
       </c>
@@ -13835,7 +14083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="A14" s="7">
         <v>46127</v>
       </c>
@@ -13876,7 +14124,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="A15" s="7">
         <v>46134</v>
       </c>
@@ -13917,7 +14165,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="A16" s="7">
         <v>46141</v>
       </c>
@@ -13958,7 +14206,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="7">
         <v>46155</v>
       </c>
@@ -13999,7 +14247,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="7">
         <v>46164</v>
       </c>
@@ -14040,7 +14288,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="7">
         <v>46169</v>
       </c>
@@ -14081,7 +14329,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="7">
         <v>46176</v>
       </c>
@@ -14122,7 +14370,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="7">
         <v>46183</v>
       </c>
@@ -14163,7 +14411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="7">
         <v>46190</v>
       </c>
@@ -14204,7 +14452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="7">
         <v>46197</v>
       </c>
@@ -14245,7 +14493,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="7">
         <v>46204</v>
       </c>
@@ -14286,7 +14534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="7">
         <v>46211</v>
       </c>
@@ -14327,7 +14575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="7">
         <v>46218</v>
       </c>
@@ -14368,7 +14616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="7">
         <v>46225</v>
       </c>
@@ -14409,7 +14657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="7">
         <v>46232</v>
       </c>
@@ -14450,7 +14698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="7">
         <v>46239</v>
       </c>
@@ -14491,7 +14739,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="7">
         <v>46246</v>
       </c>
@@ -14532,7 +14780,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="7">
         <v>46253</v>
       </c>
@@ -14570,6 +14818,47 @@
         <v>8</v>
       </c>
       <c r="M31" s="14">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="14">
+        <v>11</v>
+      </c>
+      <c r="F32" s="14">
+        <v>10</v>
+      </c>
+      <c r="G32" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>18</v>
+      </c>
+      <c r="I32" s="14">
+        <v>17</v>
+      </c>
+      <c r="J32" s="14">
+        <v>17</v>
+      </c>
+      <c r="K32" s="14">
+        <v>9</v>
+      </c>
+      <c r="L32" s="14">
+        <v>8</v>
+      </c>
+      <c r="M32" s="14">
         <v>8.5</v>
       </c>
     </row>
@@ -14588,7 +14877,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9750F8-1F5B-4526-B393-530CBB79CB33}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14600,18 +14889,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -14619,25 +14908,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -14645,19 +14934,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -14665,19 +14954,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -14685,13 +14974,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -14699,13 +14988,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>20</v>

--- a/data_lake/industry/TrendForce/PV.xlsx
+++ b/data_lake/industry/TrendForce/PV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45BA455-3EE6-B649-B252-2E279B61BA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2C2781-2C27-604B-8747-D9C0DE20A896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="780" windowWidth="19320" windowHeight="20760" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polysilicon" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="41">
   <si>
     <t>Item</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -494,6 +494,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -591,6 +594,9 @@
                   <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -728,6 +734,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -825,6 +834,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -962,6 +974,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1059,6 +1074,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1196,6 +1214,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1293,6 +1314,9 @@
                   <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>17.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1652,6 +1676,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1750,6 +1777,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1886,6 +1916,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1984,6 +2017,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2120,6 +2156,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2218,6 +2257,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.1000000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2577,6 +2619,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2751,6 +2796,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2925,6 +2973,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3023,6 +3074,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3383,6 +3437,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3480,6 +3537,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -3617,6 +3677,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3714,6 +3777,9 @@
                   <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -4073,6 +4139,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4170,6 +4239,9 @@
                   <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>10.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4307,6 +4379,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4404,6 +4479,9 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -4541,6 +4619,9 @@
                 <c:pt idx="29">
                   <c:v>46260</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>46267</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4638,6 +4719,9 @@
                   <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -8091,7 +8175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D1B81D-D2B5-4136-B018-10098EFAD710}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="7" bestFit="1" customWidth="1"/>
@@ -9711,6 +9795,56 @@
         <v>17.5</v>
       </c>
     </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="13">
+        <v>45</v>
+      </c>
+      <c r="F33" s="13">
+        <v>33</v>
+      </c>
+      <c r="G33" s="13">
+        <v>33.5</v>
+      </c>
+      <c r="H33" s="13">
+        <v>43</v>
+      </c>
+      <c r="I33" s="13">
+        <v>32</v>
+      </c>
+      <c r="J33" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="K33" s="13">
+        <v>41</v>
+      </c>
+      <c r="L33" s="13">
+        <v>30</v>
+      </c>
+      <c r="M33" s="13">
+        <v>31</v>
+      </c>
+      <c r="N33" s="13">
+        <v>22</v>
+      </c>
+      <c r="O33" s="14">
+        <v>13.1</v>
+      </c>
+      <c r="P33" s="14">
+        <v>17.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -9726,7 +9860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF786EB3-DEA4-49FB-B1F0-2BA953D252F0}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
@@ -11066,6 +11200,47 @@
       </c>
       <c r="M32" s="10">
         <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F33" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="G33" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="H33" s="10">
+        <v>1.18</v>
+      </c>
+      <c r="I33" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J33" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="K33" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L33" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="M33" s="10">
+        <v>1.1000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11082,7 +11257,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F6FBB9-AFC2-4455-9148-BD1E8CC7D9AD}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="7" bestFit="1" customWidth="1"/>
@@ -12422,6 +12597,47 @@
       </c>
       <c r="M32" s="10">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="F33" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="I33" s="10">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="J33" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="L33" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -12438,7 +12654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01E61-2CE9-42E3-8B86-FF77C69F477A}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -13501,6 +13717,38 @@
         <v>0.7</v>
       </c>
       <c r="J32" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F33" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I33" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J33" s="10">
         <v>0.7</v>
       </c>
     </row>
@@ -13518,7 +13766,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38928A9-57B3-4E00-9ADC-24F31F32D1A1}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -14859,6 +15107,47 @@
         <v>8</v>
       </c>
       <c r="M32" s="14">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46267</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="14">
+        <v>11</v>
+      </c>
+      <c r="F33" s="14">
+        <v>10</v>
+      </c>
+      <c r="G33" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>17.5</v>
+      </c>
+      <c r="I33" s="14">
+        <v>17</v>
+      </c>
+      <c r="J33" s="14">
+        <v>17</v>
+      </c>
+      <c r="K33" s="14">
+        <v>9</v>
+      </c>
+      <c r="L33" s="14">
+        <v>8</v>
+      </c>
+      <c r="M33" s="14">
         <v>8.5</v>
       </c>
     </row>
